--- a/docs/design/ACSMS-SCR-002/【日本農業新聞様】VTIジャパン_クラウド版購読者管理システム_API設計書_単価マスタ明細検索画面_V1.0.xlsx
+++ b/docs/design/ACSMS-SCR-002/【日本農業新聞様】VTIジャパン_クラウド版購読者管理システム_API設計書_単価マスタ明細検索画面_V1.0.xlsx
@@ -1700,7 +1700,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/04/13</t>
+          <t>2026/08/17</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -1990,7 +1990,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK12"/>
+  <dimension ref="A1:AK14"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="4.25" customWidth="1" min="1" max="1"/>
@@ -2151,7 +2151,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/04/13</t>
+          <t>2026/08/17</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -2268,7 +2268,7 @@
       <c r="B6" s="11" t="n"/>
       <c r="C6" s="19" t="inlineStr">
         <is>
-          <t>UNAUTHORIZED</t>
+          <t>共通</t>
         </is>
       </c>
       <c r="D6" s="10" t="n"/>
@@ -2279,7 +2279,7 @@
       <c r="I6" s="11" t="n"/>
       <c r="J6" s="19" t="inlineStr">
         <is>
-          <t>UNAUTHORIZED</t>
+          <t>BAD_REQUEST</t>
         </is>
       </c>
       <c r="K6" s="10" t="n"/>
@@ -2295,7 +2295,7 @@
       <c r="U6" s="11" t="n"/>
       <c r="V6" s="19" t="inlineStr">
         <is>
-          <t>セッションが切れました。再度ログインしてください。</t>
+          <t>リクエストパラメータが不正です。</t>
         </is>
       </c>
       <c r="W6" s="10" t="n"/>
@@ -2321,7 +2321,7 @@
       <c r="B7" s="11" t="n"/>
       <c r="C7" s="19" t="inlineStr">
         <is>
-          <t>FORBIDDEN</t>
+          <t>共通</t>
         </is>
       </c>
       <c r="D7" s="10" t="n"/>
@@ -2332,7 +2332,7 @@
       <c r="I7" s="11" t="n"/>
       <c r="J7" s="19" t="inlineStr">
         <is>
-          <t>FORBIDDEN</t>
+          <t>UNAUTHORIZED</t>
         </is>
       </c>
       <c r="K7" s="10" t="n"/>
@@ -2348,7 +2348,7 @@
       <c r="U7" s="11" t="n"/>
       <c r="V7" s="19" t="inlineStr">
         <is>
-          <t>この画面へのアクセス権限がありません。</t>
+          <t>セッションが切れました。再度ログインしてください。</t>
         </is>
       </c>
       <c r="W7" s="10" t="n"/>
@@ -2374,7 +2374,7 @@
       <c r="B8" s="11" t="n"/>
       <c r="C8" s="19" t="inlineStr">
         <is>
-          <t>NOT_FOUND</t>
+          <t>共通</t>
         </is>
       </c>
       <c r="D8" s="10" t="n"/>
@@ -2385,7 +2385,7 @@
       <c r="I8" s="11" t="n"/>
       <c r="J8" s="19" t="inlineStr">
         <is>
-          <t>NOT_FOUND</t>
+          <t>FORBIDDEN</t>
         </is>
       </c>
       <c r="K8" s="10" t="n"/>
@@ -2401,7 +2401,7 @@
       <c r="U8" s="11" t="n"/>
       <c r="V8" s="19" t="inlineStr">
         <is>
-          <t>指定された単価が見つかりません。</t>
+          <t>この画面へのアクセス権限がありません。</t>
         </is>
       </c>
       <c r="W8" s="10" t="n"/>
@@ -2427,7 +2427,7 @@
       <c r="B9" s="11" t="n"/>
       <c r="C9" s="19" t="inlineStr">
         <is>
-          <t>BAD_REQUEST</t>
+          <t>共通</t>
         </is>
       </c>
       <c r="D9" s="10" t="n"/>
@@ -2438,7 +2438,7 @@
       <c r="I9" s="11" t="n"/>
       <c r="J9" s="19" t="inlineStr">
         <is>
-          <t>BAD_REQUEST</t>
+          <t>DATA_SCOPE_VIOLATION</t>
         </is>
       </c>
       <c r="K9" s="10" t="n"/>
@@ -2454,7 +2454,7 @@
       <c r="U9" s="11" t="n"/>
       <c r="V9" s="19" t="inlineStr">
         <is>
-          <t>リクエストパラメータが不正です。</t>
+          <t>このデータへのアクセス権限がありません。</t>
         </is>
       </c>
       <c r="W9" s="10" t="n"/>
@@ -2480,7 +2480,7 @@
       <c r="B10" s="11" t="n"/>
       <c r="C10" s="19" t="inlineStr">
         <is>
-          <t>VALIDATION_ERROR</t>
+          <t>共通</t>
         </is>
       </c>
       <c r="D10" s="10" t="n"/>
@@ -2533,7 +2533,7 @@
       <c r="B11" s="11" t="n"/>
       <c r="C11" s="19" t="inlineStr">
         <is>
-          <t>CONFLICT</t>
+          <t>共通</t>
         </is>
       </c>
       <c r="D11" s="10" t="n"/>
@@ -2544,7 +2544,7 @@
       <c r="I11" s="11" t="n"/>
       <c r="J11" s="19" t="inlineStr">
         <is>
-          <t>CONFLICT</t>
+          <t>TOO_MANY_REQUESTS</t>
         </is>
       </c>
       <c r="K11" s="10" t="n"/>
@@ -2560,7 +2560,7 @@
       <c r="U11" s="11" t="n"/>
       <c r="V11" s="19" t="inlineStr">
         <is>
-          <t>関連データが存在するため削除できません。</t>
+          <t>リクエスト回数が上限を超えました。しばらくしてから再度お試しください。</t>
         </is>
       </c>
       <c r="W11" s="10" t="n"/>
@@ -2586,7 +2586,7 @@
       <c r="B12" s="11" t="n"/>
       <c r="C12" s="19" t="inlineStr">
         <is>
-          <t>INTERNAL_SERVER_ERROR</t>
+          <t>共通</t>
         </is>
       </c>
       <c r="D12" s="10" t="n"/>
@@ -2632,8 +2632,114 @@
       <c r="AJ12" s="10" t="n"/>
       <c r="AK12" s="11" t="n"/>
     </row>
+    <row r="13" ht="19.5" customHeight="1">
+      <c r="A13" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="B13" s="11" t="n"/>
+      <c r="C13" s="19" t="inlineStr">
+        <is>
+          <t>画面固有</t>
+        </is>
+      </c>
+      <c r="D13" s="10" t="n"/>
+      <c r="E13" s="10" t="n"/>
+      <c r="F13" s="10" t="n"/>
+      <c r="G13" s="10" t="n"/>
+      <c r="H13" s="10" t="n"/>
+      <c r="I13" s="11" t="n"/>
+      <c r="J13" s="19" t="inlineStr">
+        <is>
+          <t>NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="K13" s="10" t="n"/>
+      <c r="L13" s="10" t="n"/>
+      <c r="M13" s="10" t="n"/>
+      <c r="N13" s="10" t="n"/>
+      <c r="O13" s="10" t="n"/>
+      <c r="P13" s="10" t="n"/>
+      <c r="Q13" s="10" t="n"/>
+      <c r="R13" s="10" t="n"/>
+      <c r="S13" s="10" t="n"/>
+      <c r="T13" s="10" t="n"/>
+      <c r="U13" s="11" t="n"/>
+      <c r="V13" s="19" t="inlineStr">
+        <is>
+          <t>指定された単価が見つかりません。</t>
+        </is>
+      </c>
+      <c r="W13" s="10" t="n"/>
+      <c r="X13" s="10" t="n"/>
+      <c r="Y13" s="10" t="n"/>
+      <c r="Z13" s="10" t="n"/>
+      <c r="AA13" s="10" t="n"/>
+      <c r="AB13" s="10" t="n"/>
+      <c r="AC13" s="10" t="n"/>
+      <c r="AD13" s="10" t="n"/>
+      <c r="AE13" s="10" t="n"/>
+      <c r="AF13" s="10" t="n"/>
+      <c r="AG13" s="10" t="n"/>
+      <c r="AH13" s="10" t="n"/>
+      <c r="AI13" s="10" t="n"/>
+      <c r="AJ13" s="10" t="n"/>
+      <c r="AK13" s="11" t="n"/>
+    </row>
+    <row r="14" ht="19.5" customHeight="1">
+      <c r="A14" s="17" t="n">
+        <v>9</v>
+      </c>
+      <c r="B14" s="11" t="n"/>
+      <c r="C14" s="19" t="inlineStr">
+        <is>
+          <t>画面固有</t>
+        </is>
+      </c>
+      <c r="D14" s="10" t="n"/>
+      <c r="E14" s="10" t="n"/>
+      <c r="F14" s="10" t="n"/>
+      <c r="G14" s="10" t="n"/>
+      <c r="H14" s="10" t="n"/>
+      <c r="I14" s="11" t="n"/>
+      <c r="J14" s="19" t="inlineStr">
+        <is>
+          <t>CONFLICT</t>
+        </is>
+      </c>
+      <c r="K14" s="10" t="n"/>
+      <c r="L14" s="10" t="n"/>
+      <c r="M14" s="10" t="n"/>
+      <c r="N14" s="10" t="n"/>
+      <c r="O14" s="10" t="n"/>
+      <c r="P14" s="10" t="n"/>
+      <c r="Q14" s="10" t="n"/>
+      <c r="R14" s="10" t="n"/>
+      <c r="S14" s="10" t="n"/>
+      <c r="T14" s="10" t="n"/>
+      <c r="U14" s="11" t="n"/>
+      <c r="V14" s="19" t="inlineStr">
+        <is>
+          <t>関連データが存在するため処理を実行できません。</t>
+        </is>
+      </c>
+      <c r="W14" s="10" t="n"/>
+      <c r="X14" s="10" t="n"/>
+      <c r="Y14" s="10" t="n"/>
+      <c r="Z14" s="10" t="n"/>
+      <c r="AA14" s="10" t="n"/>
+      <c r="AB14" s="10" t="n"/>
+      <c r="AC14" s="10" t="n"/>
+      <c r="AD14" s="10" t="n"/>
+      <c r="AE14" s="10" t="n"/>
+      <c r="AF14" s="10" t="n"/>
+      <c r="AG14" s="10" t="n"/>
+      <c r="AH14" s="10" t="n"/>
+      <c r="AI14" s="10" t="n"/>
+      <c r="AJ14" s="10" t="n"/>
+      <c r="AK14" s="11" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="46">
+  <mergeCells count="54">
     <mergeCell ref="V11:AK11"/>
     <mergeCell ref="J6:U6"/>
     <mergeCell ref="C8:I8"/>
@@ -2644,6 +2750,7 @@
     <mergeCell ref="A6:B6"/>
     <mergeCell ref="V7:AK7"/>
     <mergeCell ref="J11:U11"/>
+    <mergeCell ref="C13:I13"/>
     <mergeCell ref="J7:U7"/>
     <mergeCell ref="A7:B7"/>
     <mergeCell ref="Q2:U3"/>
@@ -2655,11 +2762,15 @@
     <mergeCell ref="A12:B12"/>
     <mergeCell ref="J1:P1"/>
     <mergeCell ref="AH2:AK3"/>
+    <mergeCell ref="C14:I14"/>
     <mergeCell ref="J12:U12"/>
     <mergeCell ref="V5:AK5"/>
     <mergeCell ref="V8:AK8"/>
+    <mergeCell ref="V14:AK14"/>
     <mergeCell ref="Q1:U1"/>
     <mergeCell ref="A5:B5"/>
+    <mergeCell ref="V13:AK13"/>
+    <mergeCell ref="A14:B14"/>
     <mergeCell ref="C10:I10"/>
     <mergeCell ref="V1:Y1"/>
     <mergeCell ref="J8:U8"/>
@@ -2671,11 +2782,14 @@
     <mergeCell ref="A2:I3"/>
     <mergeCell ref="J5:U5"/>
     <mergeCell ref="C9:I9"/>
+    <mergeCell ref="J14:U14"/>
     <mergeCell ref="J10:U10"/>
     <mergeCell ref="V9:AK9"/>
     <mergeCell ref="A10:B10"/>
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="C12:I12"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="J13:U13"/>
     <mergeCell ref="V2:Y3"/>
     <mergeCell ref="V6:AK6"/>
     <mergeCell ref="C11:I11"/>
@@ -2852,7 +2966,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/04/13</t>
+          <t>2026/08/17</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -3126,7 +3240,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK107"/>
+  <dimension ref="A1:AK118"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="4.25" customWidth="1" min="1" max="1"/>
@@ -3287,7 +3401,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/04/13</t>
+          <t>2026/08/17</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -3580,7 +3694,7 @@
       <c r="AJ11" s="10" t="n"/>
       <c r="AK11" s="11" t="n"/>
     </row>
-    <row r="12" ht="36" customHeight="1">
+    <row r="12" ht="54" customHeight="1">
       <c r="B12" s="33" t="inlineStr">
         <is>
           <t>リクエストパラメーター</t>
@@ -3595,7 +3709,7 @@
       <c r="I12" s="11" t="n"/>
       <c r="J12" s="19" t="inlineStr">
         <is>
-          <t>?tanka_type={tanka_type}&amp;tanka_name={tanka_name}&amp;page={page}&amp;per_page={per_page}&amp;sort_by={sort_by}&amp;sort_order={sort_order}</t>
+          <t>?tanka_type={tanka_type}&amp;tanka_name={tanka_name}&amp;tekiyo_start_date={tekiyo_start_date}&amp;tekiyo_end_date={tekiyo_end_date}&amp;active_flg={active_flg}&amp;campaign_flg={campaign_flg}&amp;page={page}&amp;per_page={per_page}&amp;sort_by={sort_by}&amp;sort_order={sort_order}</t>
         </is>
       </c>
       <c r="K12" s="10" t="n"/>
@@ -4009,7 +4123,7 @@
       <c r="AE23" s="11" t="n"/>
       <c r="AF23" s="19" t="inlineStr">
         <is>
-          <t>単価種別（完全一致）</t>
+          <t>単価種別（完全一致）。1=新聞購読料, 2=配達手数料</t>
         </is>
       </c>
       <c r="AG23" s="10" t="n"/>
@@ -4080,13 +4194,13 @@
       <c r="AJ24" s="10" t="n"/>
       <c r="AK24" s="11" t="n"/>
     </row>
-    <row r="25" ht="18" customHeight="1">
+    <row r="25" ht="36" customHeight="1">
       <c r="B25" s="31" t="n">
         <v>3</v>
       </c>
       <c r="C25" s="19" t="inlineStr">
         <is>
-          <t>page</t>
+          <t>tekiyo_start_date</t>
         </is>
       </c>
       <c r="D25" s="10" t="n"/>
@@ -4100,7 +4214,7 @@
       <c r="L25" s="11" t="n"/>
       <c r="M25" s="17" t="inlineStr">
         <is>
-          <t>Number</t>
+          <t>String</t>
         </is>
       </c>
       <c r="N25" s="10" t="n"/>
@@ -4126,12 +4240,14 @@
       <c r="Z25" s="10" t="n"/>
       <c r="AA25" s="10" t="n"/>
       <c r="AB25" s="11" t="n"/>
-      <c r="AC25" s="17" t="inlineStr"/>
+      <c r="AC25" s="17" t="n">
+        <v>10</v>
+      </c>
       <c r="AD25" s="10" t="n"/>
       <c r="AE25" s="11" t="n"/>
       <c r="AF25" s="19" t="inlineStr">
         <is>
-          <t>ページ番号（デフォルト: 1）</t>
+          <t>適用開始日フィルタ（YYYY-MM-DD）。`tekiyo_start_date &gt;= 指定値` の条件で絞り込む</t>
         </is>
       </c>
       <c r="AG25" s="10" t="n"/>
@@ -4140,13 +4256,13 @@
       <c r="AJ25" s="10" t="n"/>
       <c r="AK25" s="11" t="n"/>
     </row>
-    <row r="26" ht="18" customHeight="1">
+    <row r="26" ht="36" customHeight="1">
       <c r="B26" s="31" t="n">
         <v>4</v>
       </c>
       <c r="C26" s="19" t="inlineStr">
         <is>
-          <t>per_page</t>
+          <t>tekiyo_end_date</t>
         </is>
       </c>
       <c r="D26" s="10" t="n"/>
@@ -4160,7 +4276,7 @@
       <c r="L26" s="11" t="n"/>
       <c r="M26" s="17" t="inlineStr">
         <is>
-          <t>Number</t>
+          <t>String</t>
         </is>
       </c>
       <c r="N26" s="10" t="n"/>
@@ -4186,12 +4302,14 @@
       <c r="Z26" s="10" t="n"/>
       <c r="AA26" s="10" t="n"/>
       <c r="AB26" s="11" t="n"/>
-      <c r="AC26" s="17" t="inlineStr"/>
+      <c r="AC26" s="17" t="n">
+        <v>10</v>
+      </c>
       <c r="AD26" s="10" t="n"/>
       <c r="AE26" s="11" t="n"/>
       <c r="AF26" s="19" t="inlineStr">
         <is>
-          <t>1ページの件数（デフォルト: 20）</t>
+          <t>適用終了日フィルタ（YYYY-MM-DD）。`tekiyo_end_date &lt;= 指定値` の条件で絞り込む。NULL（無期限）は対象外</t>
         </is>
       </c>
       <c r="AG26" s="10" t="n"/>
@@ -4200,13 +4318,13 @@
       <c r="AJ26" s="10" t="n"/>
       <c r="AK26" s="11" t="n"/>
     </row>
-    <row r="27" ht="36" customHeight="1">
+    <row r="27" ht="18" customHeight="1">
       <c r="B27" s="31" t="n">
         <v>5</v>
       </c>
       <c r="C27" s="19" t="inlineStr">
         <is>
-          <t>sort_by</t>
+          <t>active_flg</t>
         </is>
       </c>
       <c r="D27" s="10" t="n"/>
@@ -4220,7 +4338,7 @@
       <c r="L27" s="11" t="n"/>
       <c r="M27" s="17" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Boolean</t>
         </is>
       </c>
       <c r="N27" s="10" t="n"/>
@@ -4251,7 +4369,7 @@
       <c r="AE27" s="11" t="n"/>
       <c r="AF27" s="19" t="inlineStr">
         <is>
-          <t>ソート項目（m_tankaテーブルのカラム名を指定。例: tanka_code, tanka_name, kingaku_zeikomi, tekiyo_start_date）</t>
+          <t>状態フィルタ（true: 有効中のみ、false: 停止中のみ、省略: 両方）</t>
         </is>
       </c>
       <c r="AG27" s="10" t="n"/>
@@ -4266,7 +4384,7 @@
       </c>
       <c r="C28" s="19" t="inlineStr">
         <is>
-          <t>sort_order</t>
+          <t>campaign_flg</t>
         </is>
       </c>
       <c r="D28" s="10" t="n"/>
@@ -4280,7 +4398,7 @@
       <c r="L28" s="11" t="n"/>
       <c r="M28" s="17" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Boolean</t>
         </is>
       </c>
       <c r="N28" s="10" t="n"/>
@@ -4311,7 +4429,7 @@
       <c r="AE28" s="11" t="n"/>
       <c r="AF28" s="19" t="inlineStr">
         <is>
-          <t>ソート方向（asc / desc）</t>
+          <t>キャンペーンフィルタ（true: 有効のみ、false: 無効のみ、省略: 両方）</t>
         </is>
       </c>
       <c r="AG28" s="10" t="n"/>
@@ -4320,24 +4438,193 @@
       <c r="AJ28" s="10" t="n"/>
       <c r="AK28" s="11" t="n"/>
     </row>
-    <row r="29" ht="19.5" customHeight="1"/>
-    <row r="30" ht="19.5" customHeight="1">
-      <c r="A30" s="27" t="inlineStr">
-        <is>
-          <t>3.レスポンスデータ</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="19.5" customHeight="1"/>
-    <row r="32" ht="19.5" customHeight="1">
-      <c r="B32" s="30" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="C32" s="16" t="inlineStr">
-        <is>
-          <t>項目ID</t>
+    <row r="29" ht="18" customHeight="1">
+      <c r="B29" s="31" t="n">
+        <v>7</v>
+      </c>
+      <c r="C29" s="19" t="inlineStr">
+        <is>
+          <t>page</t>
+        </is>
+      </c>
+      <c r="D29" s="10" t="n"/>
+      <c r="E29" s="10" t="n"/>
+      <c r="F29" s="10" t="n"/>
+      <c r="G29" s="10" t="n"/>
+      <c r="H29" s="10" t="n"/>
+      <c r="I29" s="10" t="n"/>
+      <c r="J29" s="10" t="n"/>
+      <c r="K29" s="10" t="n"/>
+      <c r="L29" s="11" t="n"/>
+      <c r="M29" s="17" t="inlineStr">
+        <is>
+          <t>Number</t>
+        </is>
+      </c>
+      <c r="N29" s="10" t="n"/>
+      <c r="O29" s="10" t="n"/>
+      <c r="P29" s="11" t="n"/>
+      <c r="Q29" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R29" s="10" t="n"/>
+      <c r="S29" s="11" t="n"/>
+      <c r="T29" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U29" s="10" t="n"/>
+      <c r="V29" s="10" t="n"/>
+      <c r="W29" s="10" t="n"/>
+      <c r="X29" s="11" t="n"/>
+      <c r="Y29" s="17" t="inlineStr"/>
+      <c r="Z29" s="10" t="n"/>
+      <c r="AA29" s="10" t="n"/>
+      <c r="AB29" s="11" t="n"/>
+      <c r="AC29" s="17" t="inlineStr"/>
+      <c r="AD29" s="10" t="n"/>
+      <c r="AE29" s="11" t="n"/>
+      <c r="AF29" s="19" t="inlineStr">
+        <is>
+          <t>ページ番号（デフォルト: 1、1以上）</t>
+        </is>
+      </c>
+      <c r="AG29" s="10" t="n"/>
+      <c r="AH29" s="10" t="n"/>
+      <c r="AI29" s="10" t="n"/>
+      <c r="AJ29" s="10" t="n"/>
+      <c r="AK29" s="11" t="n"/>
+    </row>
+    <row r="30" ht="18" customHeight="1">
+      <c r="B30" s="31" t="n">
+        <v>8</v>
+      </c>
+      <c r="C30" s="19" t="inlineStr">
+        <is>
+          <t>per_page</t>
+        </is>
+      </c>
+      <c r="D30" s="10" t="n"/>
+      <c r="E30" s="10" t="n"/>
+      <c r="F30" s="10" t="n"/>
+      <c r="G30" s="10" t="n"/>
+      <c r="H30" s="10" t="n"/>
+      <c r="I30" s="10" t="n"/>
+      <c r="J30" s="10" t="n"/>
+      <c r="K30" s="10" t="n"/>
+      <c r="L30" s="11" t="n"/>
+      <c r="M30" s="17" t="inlineStr">
+        <is>
+          <t>Number</t>
+        </is>
+      </c>
+      <c r="N30" s="10" t="n"/>
+      <c r="O30" s="10" t="n"/>
+      <c r="P30" s="11" t="n"/>
+      <c r="Q30" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R30" s="10" t="n"/>
+      <c r="S30" s="11" t="n"/>
+      <c r="T30" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U30" s="10" t="n"/>
+      <c r="V30" s="10" t="n"/>
+      <c r="W30" s="10" t="n"/>
+      <c r="X30" s="11" t="n"/>
+      <c r="Y30" s="17" t="inlineStr"/>
+      <c r="Z30" s="10" t="n"/>
+      <c r="AA30" s="10" t="n"/>
+      <c r="AB30" s="11" t="n"/>
+      <c r="AC30" s="17" t="inlineStr"/>
+      <c r="AD30" s="10" t="n"/>
+      <c r="AE30" s="11" t="n"/>
+      <c r="AF30" s="19" t="inlineStr">
+        <is>
+          <t>1ページの件数（デフォルト: 20、最大: 100）</t>
+        </is>
+      </c>
+      <c r="AG30" s="10" t="n"/>
+      <c r="AH30" s="10" t="n"/>
+      <c r="AI30" s="10" t="n"/>
+      <c r="AJ30" s="10" t="n"/>
+      <c r="AK30" s="11" t="n"/>
+    </row>
+    <row r="31" ht="72" customHeight="1">
+      <c r="B31" s="31" t="n">
+        <v>9</v>
+      </c>
+      <c r="C31" s="19" t="inlineStr">
+        <is>
+          <t>sort_by</t>
+        </is>
+      </c>
+      <c r="D31" s="10" t="n"/>
+      <c r="E31" s="10" t="n"/>
+      <c r="F31" s="10" t="n"/>
+      <c r="G31" s="10" t="n"/>
+      <c r="H31" s="10" t="n"/>
+      <c r="I31" s="10" t="n"/>
+      <c r="J31" s="10" t="n"/>
+      <c r="K31" s="10" t="n"/>
+      <c r="L31" s="11" t="n"/>
+      <c r="M31" s="17" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="N31" s="10" t="n"/>
+      <c r="O31" s="10" t="n"/>
+      <c r="P31" s="11" t="n"/>
+      <c r="Q31" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R31" s="10" t="n"/>
+      <c r="S31" s="11" t="n"/>
+      <c r="T31" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U31" s="10" t="n"/>
+      <c r="V31" s="10" t="n"/>
+      <c r="W31" s="10" t="n"/>
+      <c r="X31" s="11" t="n"/>
+      <c r="Y31" s="17" t="inlineStr"/>
+      <c r="Z31" s="10" t="n"/>
+      <c r="AA31" s="10" t="n"/>
+      <c r="AB31" s="11" t="n"/>
+      <c r="AC31" s="17" t="inlineStr"/>
+      <c r="AD31" s="10" t="n"/>
+      <c r="AE31" s="11" t="n"/>
+      <c r="AF31" s="19" t="inlineStr">
+        <is>
+          <t>ソート項目（許可値: tanka_code, tanka_name, kingaku_zeikomi, kingaku_zeinuki, tax_rate, tekiyo_start_date, tekiyo_end_date, updated_at。デフォルト: updated_at）</t>
+        </is>
+      </c>
+      <c r="AG31" s="10" t="n"/>
+      <c r="AH31" s="10" t="n"/>
+      <c r="AI31" s="10" t="n"/>
+      <c r="AJ31" s="10" t="n"/>
+      <c r="AK31" s="11" t="n"/>
+    </row>
+    <row r="32" ht="18" customHeight="1">
+      <c r="B32" s="31" t="n">
+        <v>10</v>
+      </c>
+      <c r="C32" s="19" t="inlineStr">
+        <is>
+          <t>sort_order</t>
         </is>
       </c>
       <c r="D32" s="10" t="n"/>
@@ -4349,44 +4636,40 @@
       <c r="J32" s="10" t="n"/>
       <c r="K32" s="10" t="n"/>
       <c r="L32" s="11" t="n"/>
-      <c r="M32" s="16" t="inlineStr">
-        <is>
-          <t>タイプ</t>
+      <c r="M32" s="17" t="inlineStr">
+        <is>
+          <t>String</t>
         </is>
       </c>
       <c r="N32" s="10" t="n"/>
       <c r="O32" s="10" t="n"/>
       <c r="P32" s="11" t="n"/>
-      <c r="Q32" s="16" t="inlineStr">
-        <is>
-          <t>繰り返し</t>
+      <c r="Q32" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="R32" s="10" t="n"/>
       <c r="S32" s="11" t="n"/>
-      <c r="T32" s="16" t="inlineStr">
-        <is>
-          <t>フォーマット</t>
+      <c r="T32" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="U32" s="10" t="n"/>
       <c r="V32" s="10" t="n"/>
       <c r="W32" s="10" t="n"/>
       <c r="X32" s="11" t="n"/>
-      <c r="Y32" s="16" t="inlineStr">
-        <is>
-          <t>Nullable</t>
-        </is>
-      </c>
+      <c r="Y32" s="17" t="inlineStr"/>
       <c r="Z32" s="10" t="n"/>
       <c r="AA32" s="10" t="n"/>
-      <c r="AB32" s="10" t="n"/>
-      <c r="AC32" s="10" t="n"/>
+      <c r="AB32" s="11" t="n"/>
+      <c r="AC32" s="17" t="inlineStr"/>
       <c r="AD32" s="10" t="n"/>
       <c r="AE32" s="11" t="n"/>
-      <c r="AF32" s="16" t="inlineStr">
-        <is>
-          <t>説明</t>
+      <c r="AF32" s="19" t="inlineStr">
+        <is>
+          <t>ソート方向（asc / desc。デフォルト: desc）</t>
         </is>
       </c>
       <c r="AG32" s="10" t="n"/>
@@ -4395,188 +4678,27 @@
       <c r="AJ32" s="10" t="n"/>
       <c r="AK32" s="11" t="n"/>
     </row>
-    <row r="33" ht="18" customHeight="1">
-      <c r="B33" s="31" t="n">
-        <v>1</v>
-      </c>
-      <c r="C33" s="19" t="inlineStr">
-        <is>
-          <t>data</t>
-        </is>
-      </c>
-      <c r="D33" s="10" t="n"/>
-      <c r="E33" s="10" t="n"/>
-      <c r="F33" s="10" t="n"/>
-      <c r="G33" s="10" t="n"/>
-      <c r="H33" s="10" t="n"/>
-      <c r="I33" s="10" t="n"/>
-      <c r="J33" s="10" t="n"/>
-      <c r="K33" s="10" t="n"/>
-      <c r="L33" s="11" t="n"/>
-      <c r="M33" s="17" t="inlineStr">
-        <is>
-          <t>Array</t>
-        </is>
-      </c>
-      <c r="N33" s="10" t="n"/>
-      <c r="O33" s="10" t="n"/>
-      <c r="P33" s="11" t="n"/>
-      <c r="Q33" s="17" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="R33" s="10" t="n"/>
-      <c r="S33" s="11" t="n"/>
-      <c r="T33" s="17" t="inlineStr"/>
-      <c r="U33" s="10" t="n"/>
-      <c r="V33" s="10" t="n"/>
-      <c r="W33" s="10" t="n"/>
-      <c r="X33" s="11" t="n"/>
-      <c r="Y33" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Z33" s="10" t="n"/>
-      <c r="AA33" s="10" t="n"/>
-      <c r="AB33" s="10" t="n"/>
-      <c r="AC33" s="10" t="n"/>
-      <c r="AD33" s="10" t="n"/>
-      <c r="AE33" s="11" t="n"/>
-      <c r="AF33" s="19" t="inlineStr"/>
-      <c r="AG33" s="10" t="n"/>
-      <c r="AH33" s="10" t="n"/>
-      <c r="AI33" s="10" t="n"/>
-      <c r="AJ33" s="10" t="n"/>
-      <c r="AK33" s="11" t="n"/>
-    </row>
-    <row r="34" ht="18" customHeight="1">
-      <c r="B34" s="31" t="n">
-        <v>2</v>
-      </c>
-      <c r="C34" s="37" t="n"/>
-      <c r="D34" s="19" t="inlineStr">
-        <is>
-          <t>tanka_id</t>
-        </is>
-      </c>
-      <c r="E34" s="10" t="n"/>
-      <c r="F34" s="10" t="n"/>
-      <c r="G34" s="10" t="n"/>
-      <c r="H34" s="10" t="n"/>
-      <c r="I34" s="10" t="n"/>
-      <c r="J34" s="10" t="n"/>
-      <c r="K34" s="10" t="n"/>
-      <c r="L34" s="11" t="n"/>
-      <c r="M34" s="17" t="inlineStr">
-        <is>
-          <t>Number</t>
-        </is>
-      </c>
-      <c r="N34" s="10" t="n"/>
-      <c r="O34" s="10" t="n"/>
-      <c r="P34" s="11" t="n"/>
-      <c r="Q34" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R34" s="10" t="n"/>
-      <c r="S34" s="11" t="n"/>
-      <c r="T34" s="17" t="inlineStr"/>
-      <c r="U34" s="10" t="n"/>
-      <c r="V34" s="10" t="n"/>
-      <c r="W34" s="10" t="n"/>
-      <c r="X34" s="11" t="n"/>
-      <c r="Y34" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Z34" s="10" t="n"/>
-      <c r="AA34" s="10" t="n"/>
-      <c r="AB34" s="10" t="n"/>
-      <c r="AC34" s="10" t="n"/>
-      <c r="AD34" s="10" t="n"/>
-      <c r="AE34" s="11" t="n"/>
-      <c r="AF34" s="19" t="inlineStr"/>
-      <c r="AG34" s="10" t="n"/>
-      <c r="AH34" s="10" t="n"/>
-      <c r="AI34" s="10" t="n"/>
-      <c r="AJ34" s="10" t="n"/>
-      <c r="AK34" s="11" t="n"/>
-    </row>
-    <row r="35" ht="18" customHeight="1">
-      <c r="B35" s="31" t="n">
-        <v>3</v>
-      </c>
-      <c r="C35" s="38" t="n"/>
-      <c r="D35" s="19" t="inlineStr">
-        <is>
-          <t>tanka_type</t>
-        </is>
-      </c>
-      <c r="E35" s="10" t="n"/>
-      <c r="F35" s="10" t="n"/>
-      <c r="G35" s="10" t="n"/>
-      <c r="H35" s="10" t="n"/>
-      <c r="I35" s="10" t="n"/>
-      <c r="J35" s="10" t="n"/>
-      <c r="K35" s="10" t="n"/>
-      <c r="L35" s="11" t="n"/>
-      <c r="M35" s="17" t="inlineStr">
-        <is>
-          <t>Number</t>
-        </is>
-      </c>
-      <c r="N35" s="10" t="n"/>
-      <c r="O35" s="10" t="n"/>
-      <c r="P35" s="11" t="n"/>
-      <c r="Q35" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R35" s="10" t="n"/>
-      <c r="S35" s="11" t="n"/>
-      <c r="T35" s="17" t="inlineStr"/>
-      <c r="U35" s="10" t="n"/>
-      <c r="V35" s="10" t="n"/>
-      <c r="W35" s="10" t="n"/>
-      <c r="X35" s="11" t="n"/>
-      <c r="Y35" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Z35" s="10" t="n"/>
-      <c r="AA35" s="10" t="n"/>
-      <c r="AB35" s="10" t="n"/>
-      <c r="AC35" s="10" t="n"/>
-      <c r="AD35" s="10" t="n"/>
-      <c r="AE35" s="11" t="n"/>
-      <c r="AF35" s="19" t="inlineStr">
-        <is>
-          <t>1: 新聞購読料, 2: 配達手数料</t>
-        </is>
-      </c>
-      <c r="AG35" s="10" t="n"/>
-      <c r="AH35" s="10" t="n"/>
-      <c r="AI35" s="10" t="n"/>
-      <c r="AJ35" s="10" t="n"/>
-      <c r="AK35" s="11" t="n"/>
-    </row>
-    <row r="36" ht="18" customHeight="1">
-      <c r="B36" s="31" t="n">
-        <v>4</v>
-      </c>
-      <c r="C36" s="38" t="n"/>
-      <c r="D36" s="19" t="inlineStr">
-        <is>
-          <t>tanka_type_label</t>
-        </is>
-      </c>
+    <row r="33" ht="19.5" customHeight="1"/>
+    <row r="34" ht="19.5" customHeight="1">
+      <c r="A34" s="27" t="inlineStr">
+        <is>
+          <t>3.レスポンスデータ</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="19.5" customHeight="1"/>
+    <row r="36" ht="19.5" customHeight="1">
+      <c r="B36" s="30" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="C36" s="16" t="inlineStr">
+        <is>
+          <t>項目ID</t>
+        </is>
+      </c>
+      <c r="D36" s="10" t="n"/>
       <c r="E36" s="10" t="n"/>
       <c r="F36" s="10" t="n"/>
       <c r="G36" s="10" t="n"/>
@@ -4585,29 +4707,33 @@
       <c r="J36" s="10" t="n"/>
       <c r="K36" s="10" t="n"/>
       <c r="L36" s="11" t="n"/>
-      <c r="M36" s="17" t="inlineStr">
-        <is>
-          <t>String</t>
+      <c r="M36" s="16" t="inlineStr">
+        <is>
+          <t>タイプ</t>
         </is>
       </c>
       <c r="N36" s="10" t="n"/>
       <c r="O36" s="10" t="n"/>
       <c r="P36" s="11" t="n"/>
-      <c r="Q36" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="Q36" s="16" t="inlineStr">
+        <is>
+          <t>繰り返し</t>
         </is>
       </c>
       <c r="R36" s="10" t="n"/>
       <c r="S36" s="11" t="n"/>
-      <c r="T36" s="17" t="inlineStr"/>
+      <c r="T36" s="16" t="inlineStr">
+        <is>
+          <t>フォーマット</t>
+        </is>
+      </c>
       <c r="U36" s="10" t="n"/>
       <c r="V36" s="10" t="n"/>
       <c r="W36" s="10" t="n"/>
       <c r="X36" s="11" t="n"/>
-      <c r="Y36" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="Y36" s="16" t="inlineStr">
+        <is>
+          <t>Nullable</t>
         </is>
       </c>
       <c r="Z36" s="10" t="n"/>
@@ -4616,9 +4742,9 @@
       <c r="AC36" s="10" t="n"/>
       <c r="AD36" s="10" t="n"/>
       <c r="AE36" s="11" t="n"/>
-      <c r="AF36" s="19" t="inlineStr">
-        <is>
-          <t>tanka_typeのラベル</t>
+      <c r="AF36" s="16" t="inlineStr">
+        <is>
+          <t>説明</t>
         </is>
       </c>
       <c r="AG36" s="10" t="n"/>
@@ -4629,14 +4755,14 @@
     </row>
     <row r="37" ht="18" customHeight="1">
       <c r="B37" s="31" t="n">
-        <v>5</v>
-      </c>
-      <c r="C37" s="38" t="n"/>
-      <c r="D37" s="19" t="inlineStr">
-        <is>
-          <t>tanka_code</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="C37" s="19" t="inlineStr">
+        <is>
+          <t>data</t>
+        </is>
+      </c>
+      <c r="D37" s="10" t="n"/>
       <c r="E37" s="10" t="n"/>
       <c r="F37" s="10" t="n"/>
       <c r="G37" s="10" t="n"/>
@@ -4647,7 +4773,7 @@
       <c r="L37" s="11" t="n"/>
       <c r="M37" s="17" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Array</t>
         </is>
       </c>
       <c r="N37" s="10" t="n"/>
@@ -4655,7 +4781,7 @@
       <c r="P37" s="11" t="n"/>
       <c r="Q37" s="17" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>〇</t>
         </is>
       </c>
       <c r="R37" s="10" t="n"/>
@@ -4685,12 +4811,12 @@
     </row>
     <row r="38" ht="18" customHeight="1">
       <c r="B38" s="31" t="n">
-        <v>6</v>
-      </c>
-      <c r="C38" s="38" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="C38" s="37" t="n"/>
       <c r="D38" s="19" t="inlineStr">
         <is>
-          <t>tanka_name</t>
+          <t>tanka_id</t>
         </is>
       </c>
       <c r="E38" s="10" t="n"/>
@@ -4703,7 +4829,7 @@
       <c r="L38" s="11" t="n"/>
       <c r="M38" s="17" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Number</t>
         </is>
       </c>
       <c r="N38" s="10" t="n"/>
@@ -4739,14 +4865,14 @@
       <c r="AJ38" s="10" t="n"/>
       <c r="AK38" s="11" t="n"/>
     </row>
-    <row r="39" ht="18" customHeight="1">
+    <row r="39" ht="54" customHeight="1">
       <c r="B39" s="31" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C39" s="38" t="n"/>
       <c r="D39" s="19" t="inlineStr">
         <is>
-          <t>kingaku_zeikomi</t>
+          <t>tanka_type</t>
         </is>
       </c>
       <c r="E39" s="10" t="n"/>
@@ -4790,7 +4916,7 @@
       <c r="AE39" s="11" t="n"/>
       <c r="AF39" s="19" t="inlineStr">
         <is>
-          <t>税込金額（円）</t>
+          <t>1: 新聞購読料, 2: 配達手数料（ラベルはFE側で `useCodesStore().label('TANKA_TYPE', value)` から取得）</t>
         </is>
       </c>
       <c r="AG39" s="10" t="n"/>
@@ -4801,12 +4927,12 @@
     </row>
     <row r="40" ht="18" customHeight="1">
       <c r="B40" s="31" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C40" s="38" t="n"/>
       <c r="D40" s="19" t="inlineStr">
         <is>
-          <t>kingaku_zeinuki</t>
+          <t>tanka_code</t>
         </is>
       </c>
       <c r="E40" s="10" t="n"/>
@@ -4819,7 +4945,7 @@
       <c r="L40" s="11" t="n"/>
       <c r="M40" s="17" t="inlineStr">
         <is>
-          <t>Number</t>
+          <t>String</t>
         </is>
       </c>
       <c r="N40" s="10" t="n"/>
@@ -4848,11 +4974,7 @@
       <c r="AC40" s="10" t="n"/>
       <c r="AD40" s="10" t="n"/>
       <c r="AE40" s="11" t="n"/>
-      <c r="AF40" s="19" t="inlineStr">
-        <is>
-          <t>税抜金額（円）</t>
-        </is>
-      </c>
+      <c r="AF40" s="19" t="inlineStr"/>
       <c r="AG40" s="10" t="n"/>
       <c r="AH40" s="10" t="n"/>
       <c r="AI40" s="10" t="n"/>
@@ -4861,12 +4983,12 @@
     </row>
     <row r="41" ht="18" customHeight="1">
       <c r="B41" s="31" t="n">
-        <v>9</v>
-      </c>
-      <c r="C41" s="39" t="n"/>
+        <v>5</v>
+      </c>
+      <c r="C41" s="38" t="n"/>
       <c r="D41" s="19" t="inlineStr">
         <is>
-          <t>tax_rate</t>
+          <t>tanka_name</t>
         </is>
       </c>
       <c r="E41" s="10" t="n"/>
@@ -4879,7 +5001,7 @@
       <c r="L41" s="11" t="n"/>
       <c r="M41" s="17" t="inlineStr">
         <is>
-          <t>Number</t>
+          <t>String</t>
         </is>
       </c>
       <c r="N41" s="10" t="n"/>
@@ -4892,11 +5014,7 @@
       </c>
       <c r="R41" s="10" t="n"/>
       <c r="S41" s="11" t="n"/>
-      <c r="T41" s="17" t="inlineStr">
-        <is>
-          <t>##.##</t>
-        </is>
-      </c>
+      <c r="T41" s="17" t="inlineStr"/>
       <c r="U41" s="10" t="n"/>
       <c r="V41" s="10" t="n"/>
       <c r="W41" s="10" t="n"/>
@@ -4912,11 +5030,7 @@
       <c r="AC41" s="10" t="n"/>
       <c r="AD41" s="10" t="n"/>
       <c r="AE41" s="11" t="n"/>
-      <c r="AF41" s="19" t="inlineStr">
-        <is>
-          <t>税率（%）</t>
-        </is>
-      </c>
+      <c r="AF41" s="19" t="inlineStr"/>
       <c r="AG41" s="10" t="n"/>
       <c r="AH41" s="10" t="n"/>
       <c r="AI41" s="10" t="n"/>
@@ -4925,14 +5039,14 @@
     </row>
     <row r="42" ht="18" customHeight="1">
       <c r="B42" s="31" t="n">
-        <v>10</v>
-      </c>
-      <c r="C42" s="19" t="inlineStr">
-        <is>
-          <t>meta</t>
-        </is>
-      </c>
-      <c r="D42" s="10" t="n"/>
+        <v>6</v>
+      </c>
+      <c r="C42" s="38" t="n"/>
+      <c r="D42" s="19" t="inlineStr">
+        <is>
+          <t>tekiyo_start_date</t>
+        </is>
+      </c>
       <c r="E42" s="10" t="n"/>
       <c r="F42" s="10" t="n"/>
       <c r="G42" s="10" t="n"/>
@@ -4943,7 +5057,7 @@
       <c r="L42" s="11" t="n"/>
       <c r="M42" s="17" t="inlineStr">
         <is>
-          <t>Object</t>
+          <t>String</t>
         </is>
       </c>
       <c r="N42" s="10" t="n"/>
@@ -4956,7 +5070,11 @@
       </c>
       <c r="R42" s="10" t="n"/>
       <c r="S42" s="11" t="n"/>
-      <c r="T42" s="17" t="inlineStr"/>
+      <c r="T42" s="17" t="inlineStr">
+        <is>
+          <t>YYYY-MM-DD</t>
+        </is>
+      </c>
       <c r="U42" s="10" t="n"/>
       <c r="V42" s="10" t="n"/>
       <c r="W42" s="10" t="n"/>
@@ -4972,7 +5090,11 @@
       <c r="AC42" s="10" t="n"/>
       <c r="AD42" s="10" t="n"/>
       <c r="AE42" s="11" t="n"/>
-      <c r="AF42" s="19" t="inlineStr"/>
+      <c r="AF42" s="19" t="inlineStr">
+        <is>
+          <t>適用開始日</t>
+        </is>
+      </c>
       <c r="AG42" s="10" t="n"/>
       <c r="AH42" s="10" t="n"/>
       <c r="AI42" s="10" t="n"/>
@@ -4981,12 +5103,12 @@
     </row>
     <row r="43" ht="18" customHeight="1">
       <c r="B43" s="31" t="n">
-        <v>11</v>
-      </c>
-      <c r="C43" s="37" t="n"/>
+        <v>7</v>
+      </c>
+      <c r="C43" s="38" t="n"/>
       <c r="D43" s="19" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>tekiyo_end_date</t>
         </is>
       </c>
       <c r="E43" s="10" t="n"/>
@@ -4999,7 +5121,7 @@
       <c r="L43" s="11" t="n"/>
       <c r="M43" s="17" t="inlineStr">
         <is>
-          <t>Number</t>
+          <t>String</t>
         </is>
       </c>
       <c r="N43" s="10" t="n"/>
@@ -5012,14 +5134,18 @@
       </c>
       <c r="R43" s="10" t="n"/>
       <c r="S43" s="11" t="n"/>
-      <c r="T43" s="17" t="inlineStr"/>
+      <c r="T43" s="17" t="inlineStr">
+        <is>
+          <t>YYYY-MM-DD</t>
+        </is>
+      </c>
       <c r="U43" s="10" t="n"/>
       <c r="V43" s="10" t="n"/>
       <c r="W43" s="10" t="n"/>
       <c r="X43" s="11" t="n"/>
       <c r="Y43" s="17" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>〇</t>
         </is>
       </c>
       <c r="Z43" s="10" t="n"/>
@@ -5030,7 +5156,7 @@
       <c r="AE43" s="11" t="n"/>
       <c r="AF43" s="19" t="inlineStr">
         <is>
-          <t>総件数</t>
+          <t>適用終了日（NULL=無期限）</t>
         </is>
       </c>
       <c r="AG43" s="10" t="n"/>
@@ -5041,12 +5167,12 @@
     </row>
     <row r="44" ht="18" customHeight="1">
       <c r="B44" s="31" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C44" s="38" t="n"/>
       <c r="D44" s="19" t="inlineStr">
         <is>
-          <t>page</t>
+          <t>kingaku_zeikomi</t>
         </is>
       </c>
       <c r="E44" s="10" t="n"/>
@@ -5090,7 +5216,7 @@
       <c r="AE44" s="11" t="n"/>
       <c r="AF44" s="19" t="inlineStr">
         <is>
-          <t>現在のページ番号</t>
+          <t>税込金額（円）</t>
         </is>
       </c>
       <c r="AG44" s="10" t="n"/>
@@ -5101,12 +5227,12 @@
     </row>
     <row r="45" ht="18" customHeight="1">
       <c r="B45" s="31" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C45" s="38" t="n"/>
       <c r="D45" s="19" t="inlineStr">
         <is>
-          <t>per_page</t>
+          <t>kingaku_zeinuki</t>
         </is>
       </c>
       <c r="E45" s="10" t="n"/>
@@ -5150,7 +5276,7 @@
       <c r="AE45" s="11" t="n"/>
       <c r="AF45" s="19" t="inlineStr">
         <is>
-          <t>1ページの件数</t>
+          <t>税抜金額（円）</t>
         </is>
       </c>
       <c r="AG45" s="10" t="n"/>
@@ -5161,12 +5287,12 @@
     </row>
     <row r="46" ht="18" customHeight="1">
       <c r="B46" s="31" t="n">
-        <v>14</v>
-      </c>
-      <c r="C46" s="39" t="n"/>
+        <v>10</v>
+      </c>
+      <c r="C46" s="38" t="n"/>
       <c r="D46" s="19" t="inlineStr">
         <is>
-          <t>total_pages</t>
+          <t>tax_rate</t>
         </is>
       </c>
       <c r="E46" s="10" t="n"/>
@@ -5192,7 +5318,11 @@
       </c>
       <c r="R46" s="10" t="n"/>
       <c r="S46" s="11" t="n"/>
-      <c r="T46" s="17" t="inlineStr"/>
+      <c r="T46" s="17" t="inlineStr">
+        <is>
+          <t>##.##</t>
+        </is>
+      </c>
       <c r="U46" s="10" t="n"/>
       <c r="V46" s="10" t="n"/>
       <c r="W46" s="10" t="n"/>
@@ -5210,7 +5340,7 @@
       <c r="AE46" s="11" t="n"/>
       <c r="AF46" s="19" t="inlineStr">
         <is>
-          <t>総ページ数</t>
+          <t>税率（%）</t>
         </is>
       </c>
       <c r="AG46" s="10" t="n"/>
@@ -5219,18 +5349,133 @@
       <c r="AJ46" s="10" t="n"/>
       <c r="AK46" s="11" t="n"/>
     </row>
-    <row r="47" ht="19.5" customHeight="1"/>
-    <row r="48" ht="19.5" customHeight="1">
-      <c r="B48" s="40" t="inlineStr">
-        <is>
-          <t>リクエスト</t>
-        </is>
-      </c>
+    <row r="47" ht="18" customHeight="1">
+      <c r="B47" s="31" t="n">
+        <v>11</v>
+      </c>
+      <c r="C47" s="38" t="n"/>
+      <c r="D47" s="19" t="inlineStr">
+        <is>
+          <t>active_flg</t>
+        </is>
+      </c>
+      <c r="E47" s="10" t="n"/>
+      <c r="F47" s="10" t="n"/>
+      <c r="G47" s="10" t="n"/>
+      <c r="H47" s="10" t="n"/>
+      <c r="I47" s="10" t="n"/>
+      <c r="J47" s="10" t="n"/>
+      <c r="K47" s="10" t="n"/>
+      <c r="L47" s="11" t="n"/>
+      <c r="M47" s="17" t="inlineStr">
+        <is>
+          <t>Boolean</t>
+        </is>
+      </c>
+      <c r="N47" s="10" t="n"/>
+      <c r="O47" s="10" t="n"/>
+      <c r="P47" s="11" t="n"/>
+      <c r="Q47" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R47" s="10" t="n"/>
+      <c r="S47" s="11" t="n"/>
+      <c r="T47" s="17" t="inlineStr"/>
+      <c r="U47" s="10" t="n"/>
+      <c r="V47" s="10" t="n"/>
+      <c r="W47" s="10" t="n"/>
+      <c r="X47" s="11" t="n"/>
+      <c r="Y47" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z47" s="10" t="n"/>
+      <c r="AA47" s="10" t="n"/>
+      <c r="AB47" s="10" t="n"/>
+      <c r="AC47" s="10" t="n"/>
+      <c r="AD47" s="10" t="n"/>
+      <c r="AE47" s="11" t="n"/>
+      <c r="AF47" s="19" t="inlineStr">
+        <is>
+          <t>運用上の有効フラグ</t>
+        </is>
+      </c>
+      <c r="AG47" s="10" t="n"/>
+      <c r="AH47" s="10" t="n"/>
+      <c r="AI47" s="10" t="n"/>
+      <c r="AJ47" s="10" t="n"/>
+      <c r="AK47" s="11" t="n"/>
+    </row>
+    <row r="48" ht="18" customHeight="1">
+      <c r="B48" s="31" t="n">
+        <v>12</v>
+      </c>
+      <c r="C48" s="39" t="n"/>
+      <c r="D48" s="19" t="inlineStr">
+        <is>
+          <t>campaign_flg</t>
+        </is>
+      </c>
+      <c r="E48" s="10" t="n"/>
+      <c r="F48" s="10" t="n"/>
+      <c r="G48" s="10" t="n"/>
+      <c r="H48" s="10" t="n"/>
+      <c r="I48" s="10" t="n"/>
+      <c r="J48" s="10" t="n"/>
+      <c r="K48" s="10" t="n"/>
+      <c r="L48" s="11" t="n"/>
+      <c r="M48" s="17" t="inlineStr">
+        <is>
+          <t>Boolean</t>
+        </is>
+      </c>
+      <c r="N48" s="10" t="n"/>
+      <c r="O48" s="10" t="n"/>
+      <c r="P48" s="11" t="n"/>
+      <c r="Q48" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R48" s="10" t="n"/>
+      <c r="S48" s="11" t="n"/>
+      <c r="T48" s="17" t="inlineStr"/>
+      <c r="U48" s="10" t="n"/>
+      <c r="V48" s="10" t="n"/>
+      <c r="W48" s="10" t="n"/>
+      <c r="X48" s="11" t="n"/>
+      <c r="Y48" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z48" s="10" t="n"/>
+      <c r="AA48" s="10" t="n"/>
+      <c r="AB48" s="10" t="n"/>
+      <c r="AC48" s="10" t="n"/>
+      <c r="AD48" s="10" t="n"/>
+      <c r="AE48" s="11" t="n"/>
+      <c r="AF48" s="19" t="inlineStr">
+        <is>
+          <t>キャンペーンフラグ（TRUE: 有効, FALSE: 無効）</t>
+        </is>
+      </c>
+      <c r="AG48" s="10" t="n"/>
+      <c r="AH48" s="10" t="n"/>
+      <c r="AI48" s="10" t="n"/>
+      <c r="AJ48" s="10" t="n"/>
+      <c r="AK48" s="11" t="n"/>
     </row>
     <row r="49" ht="18" customHeight="1">
+      <c r="B49" s="31" t="n">
+        <v>13</v>
+      </c>
       <c r="C49" s="19" t="inlineStr">
         <is>
-          <t>GET /api/v1/tanka?tanka_type=1&amp;tanka_name=基本&amp;page=1&amp;per_page=20&amp;sort_by=tanka_code&amp;sort_order=asc</t>
+          <t>meta</t>
         </is>
       </c>
       <c r="D49" s="10" t="n"/>
@@ -5241,54 +5486,358 @@
       <c r="I49" s="10" t="n"/>
       <c r="J49" s="10" t="n"/>
       <c r="K49" s="10" t="n"/>
-      <c r="L49" s="10" t="n"/>
-      <c r="M49" s="10" t="n"/>
+      <c r="L49" s="11" t="n"/>
+      <c r="M49" s="17" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
       <c r="N49" s="10" t="n"/>
       <c r="O49" s="10" t="n"/>
-      <c r="P49" s="10" t="n"/>
-      <c r="Q49" s="10" t="n"/>
+      <c r="P49" s="11" t="n"/>
+      <c r="Q49" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="R49" s="10" t="n"/>
-      <c r="S49" s="10" t="n"/>
-      <c r="T49" s="10" t="n"/>
+      <c r="S49" s="11" t="n"/>
+      <c r="T49" s="17" t="inlineStr"/>
       <c r="U49" s="10" t="n"/>
       <c r="V49" s="10" t="n"/>
       <c r="W49" s="10" t="n"/>
-      <c r="X49" s="10" t="n"/>
-      <c r="Y49" s="10" t="n"/>
+      <c r="X49" s="11" t="n"/>
+      <c r="Y49" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="Z49" s="10" t="n"/>
       <c r="AA49" s="10" t="n"/>
       <c r="AB49" s="10" t="n"/>
       <c r="AC49" s="10" t="n"/>
       <c r="AD49" s="10" t="n"/>
-      <c r="AE49" s="10" t="n"/>
-      <c r="AF49" s="10" t="n"/>
+      <c r="AE49" s="11" t="n"/>
+      <c r="AF49" s="19" t="inlineStr"/>
       <c r="AG49" s="10" t="n"/>
       <c r="AH49" s="10" t="n"/>
       <c r="AI49" s="10" t="n"/>
       <c r="AJ49" s="10" t="n"/>
       <c r="AK49" s="11" t="n"/>
     </row>
-    <row r="51" ht="19.5" customHeight="1">
-      <c r="B51" s="40" t="inlineStr">
+    <row r="50" ht="18" customHeight="1">
+      <c r="B50" s="31" t="n">
+        <v>14</v>
+      </c>
+      <c r="C50" s="37" t="n"/>
+      <c r="D50" s="19" t="inlineStr">
+        <is>
+          <t>total</t>
+        </is>
+      </c>
+      <c r="E50" s="10" t="n"/>
+      <c r="F50" s="10" t="n"/>
+      <c r="G50" s="10" t="n"/>
+      <c r="H50" s="10" t="n"/>
+      <c r="I50" s="10" t="n"/>
+      <c r="J50" s="10" t="n"/>
+      <c r="K50" s="10" t="n"/>
+      <c r="L50" s="11" t="n"/>
+      <c r="M50" s="17" t="inlineStr">
+        <is>
+          <t>Number</t>
+        </is>
+      </c>
+      <c r="N50" s="10" t="n"/>
+      <c r="O50" s="10" t="n"/>
+      <c r="P50" s="11" t="n"/>
+      <c r="Q50" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R50" s="10" t="n"/>
+      <c r="S50" s="11" t="n"/>
+      <c r="T50" s="17" t="inlineStr"/>
+      <c r="U50" s="10" t="n"/>
+      <c r="V50" s="10" t="n"/>
+      <c r="W50" s="10" t="n"/>
+      <c r="X50" s="11" t="n"/>
+      <c r="Y50" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z50" s="10" t="n"/>
+      <c r="AA50" s="10" t="n"/>
+      <c r="AB50" s="10" t="n"/>
+      <c r="AC50" s="10" t="n"/>
+      <c r="AD50" s="10" t="n"/>
+      <c r="AE50" s="11" t="n"/>
+      <c r="AF50" s="19" t="inlineStr">
+        <is>
+          <t>総件数</t>
+        </is>
+      </c>
+      <c r="AG50" s="10" t="n"/>
+      <c r="AH50" s="10" t="n"/>
+      <c r="AI50" s="10" t="n"/>
+      <c r="AJ50" s="10" t="n"/>
+      <c r="AK50" s="11" t="n"/>
+    </row>
+    <row r="51" ht="18" customHeight="1">
+      <c r="B51" s="31" t="n">
+        <v>15</v>
+      </c>
+      <c r="C51" s="38" t="n"/>
+      <c r="D51" s="19" t="inlineStr">
+        <is>
+          <t>page</t>
+        </is>
+      </c>
+      <c r="E51" s="10" t="n"/>
+      <c r="F51" s="10" t="n"/>
+      <c r="G51" s="10" t="n"/>
+      <c r="H51" s="10" t="n"/>
+      <c r="I51" s="10" t="n"/>
+      <c r="J51" s="10" t="n"/>
+      <c r="K51" s="10" t="n"/>
+      <c r="L51" s="11" t="n"/>
+      <c r="M51" s="17" t="inlineStr">
+        <is>
+          <t>Number</t>
+        </is>
+      </c>
+      <c r="N51" s="10" t="n"/>
+      <c r="O51" s="10" t="n"/>
+      <c r="P51" s="11" t="n"/>
+      <c r="Q51" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R51" s="10" t="n"/>
+      <c r="S51" s="11" t="n"/>
+      <c r="T51" s="17" t="inlineStr"/>
+      <c r="U51" s="10" t="n"/>
+      <c r="V51" s="10" t="n"/>
+      <c r="W51" s="10" t="n"/>
+      <c r="X51" s="11" t="n"/>
+      <c r="Y51" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z51" s="10" t="n"/>
+      <c r="AA51" s="10" t="n"/>
+      <c r="AB51" s="10" t="n"/>
+      <c r="AC51" s="10" t="n"/>
+      <c r="AD51" s="10" t="n"/>
+      <c r="AE51" s="11" t="n"/>
+      <c r="AF51" s="19" t="inlineStr">
+        <is>
+          <t>現在のページ番号</t>
+        </is>
+      </c>
+      <c r="AG51" s="10" t="n"/>
+      <c r="AH51" s="10" t="n"/>
+      <c r="AI51" s="10" t="n"/>
+      <c r="AJ51" s="10" t="n"/>
+      <c r="AK51" s="11" t="n"/>
+    </row>
+    <row r="52" ht="18" customHeight="1">
+      <c r="B52" s="31" t="n">
+        <v>16</v>
+      </c>
+      <c r="C52" s="38" t="n"/>
+      <c r="D52" s="19" t="inlineStr">
+        <is>
+          <t>per_page</t>
+        </is>
+      </c>
+      <c r="E52" s="10" t="n"/>
+      <c r="F52" s="10" t="n"/>
+      <c r="G52" s="10" t="n"/>
+      <c r="H52" s="10" t="n"/>
+      <c r="I52" s="10" t="n"/>
+      <c r="J52" s="10" t="n"/>
+      <c r="K52" s="10" t="n"/>
+      <c r="L52" s="11" t="n"/>
+      <c r="M52" s="17" t="inlineStr">
+        <is>
+          <t>Number</t>
+        </is>
+      </c>
+      <c r="N52" s="10" t="n"/>
+      <c r="O52" s="10" t="n"/>
+      <c r="P52" s="11" t="n"/>
+      <c r="Q52" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R52" s="10" t="n"/>
+      <c r="S52" s="11" t="n"/>
+      <c r="T52" s="17" t="inlineStr"/>
+      <c r="U52" s="10" t="n"/>
+      <c r="V52" s="10" t="n"/>
+      <c r="W52" s="10" t="n"/>
+      <c r="X52" s="11" t="n"/>
+      <c r="Y52" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z52" s="10" t="n"/>
+      <c r="AA52" s="10" t="n"/>
+      <c r="AB52" s="10" t="n"/>
+      <c r="AC52" s="10" t="n"/>
+      <c r="AD52" s="10" t="n"/>
+      <c r="AE52" s="11" t="n"/>
+      <c r="AF52" s="19" t="inlineStr">
+        <is>
+          <t>1ページの件数</t>
+        </is>
+      </c>
+      <c r="AG52" s="10" t="n"/>
+      <c r="AH52" s="10" t="n"/>
+      <c r="AI52" s="10" t="n"/>
+      <c r="AJ52" s="10" t="n"/>
+      <c r="AK52" s="11" t="n"/>
+    </row>
+    <row r="53" ht="18" customHeight="1">
+      <c r="B53" s="31" t="n">
+        <v>17</v>
+      </c>
+      <c r="C53" s="39" t="n"/>
+      <c r="D53" s="19" t="inlineStr">
+        <is>
+          <t>total_pages</t>
+        </is>
+      </c>
+      <c r="E53" s="10" t="n"/>
+      <c r="F53" s="10" t="n"/>
+      <c r="G53" s="10" t="n"/>
+      <c r="H53" s="10" t="n"/>
+      <c r="I53" s="10" t="n"/>
+      <c r="J53" s="10" t="n"/>
+      <c r="K53" s="10" t="n"/>
+      <c r="L53" s="11" t="n"/>
+      <c r="M53" s="17" t="inlineStr">
+        <is>
+          <t>Number</t>
+        </is>
+      </c>
+      <c r="N53" s="10" t="n"/>
+      <c r="O53" s="10" t="n"/>
+      <c r="P53" s="11" t="n"/>
+      <c r="Q53" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R53" s="10" t="n"/>
+      <c r="S53" s="11" t="n"/>
+      <c r="T53" s="17" t="inlineStr"/>
+      <c r="U53" s="10" t="n"/>
+      <c r="V53" s="10" t="n"/>
+      <c r="W53" s="10" t="n"/>
+      <c r="X53" s="11" t="n"/>
+      <c r="Y53" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z53" s="10" t="n"/>
+      <c r="AA53" s="10" t="n"/>
+      <c r="AB53" s="10" t="n"/>
+      <c r="AC53" s="10" t="n"/>
+      <c r="AD53" s="10" t="n"/>
+      <c r="AE53" s="11" t="n"/>
+      <c r="AF53" s="19" t="inlineStr">
+        <is>
+          <t>総ページ数</t>
+        </is>
+      </c>
+      <c r="AG53" s="10" t="n"/>
+      <c r="AH53" s="10" t="n"/>
+      <c r="AI53" s="10" t="n"/>
+      <c r="AJ53" s="10" t="n"/>
+      <c r="AK53" s="11" t="n"/>
+    </row>
+    <row r="54" ht="19.5" customHeight="1"/>
+    <row r="55" ht="19.5" customHeight="1">
+      <c r="B55" s="40" t="inlineStr">
+        <is>
+          <t>リクエスト</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="18" customHeight="1">
+      <c r="C56" s="19" t="inlineStr">
+        <is>
+          <t>GET /api/v1/tanka?tanka_type=1&amp;tanka_name=基本&amp;tekiyo_start_date=2026-04-01&amp;tekiyo_end_date=2027-03-31&amp;page=1&amp;per_page=20&amp;sort_by=tanka_code&amp;sort_order=asc</t>
+        </is>
+      </c>
+      <c r="D56" s="10" t="n"/>
+      <c r="E56" s="10" t="n"/>
+      <c r="F56" s="10" t="n"/>
+      <c r="G56" s="10" t="n"/>
+      <c r="H56" s="10" t="n"/>
+      <c r="I56" s="10" t="n"/>
+      <c r="J56" s="10" t="n"/>
+      <c r="K56" s="10" t="n"/>
+      <c r="L56" s="10" t="n"/>
+      <c r="M56" s="10" t="n"/>
+      <c r="N56" s="10" t="n"/>
+      <c r="O56" s="10" t="n"/>
+      <c r="P56" s="10" t="n"/>
+      <c r="Q56" s="10" t="n"/>
+      <c r="R56" s="10" t="n"/>
+      <c r="S56" s="10" t="n"/>
+      <c r="T56" s="10" t="n"/>
+      <c r="U56" s="10" t="n"/>
+      <c r="V56" s="10" t="n"/>
+      <c r="W56" s="10" t="n"/>
+      <c r="X56" s="10" t="n"/>
+      <c r="Y56" s="10" t="n"/>
+      <c r="Z56" s="10" t="n"/>
+      <c r="AA56" s="10" t="n"/>
+      <c r="AB56" s="10" t="n"/>
+      <c r="AC56" s="10" t="n"/>
+      <c r="AD56" s="10" t="n"/>
+      <c r="AE56" s="10" t="n"/>
+      <c r="AF56" s="10" t="n"/>
+      <c r="AG56" s="10" t="n"/>
+      <c r="AH56" s="10" t="n"/>
+      <c r="AI56" s="10" t="n"/>
+      <c r="AJ56" s="10" t="n"/>
+      <c r="AK56" s="11" t="n"/>
+    </row>
+    <row r="58" ht="19.5" customHeight="1">
+      <c r="B58" s="40" t="inlineStr">
         <is>
           <t>レスポンス（成功）</t>
         </is>
       </c>
     </row>
-    <row r="52" ht="360" customHeight="1">
-      <c r="C52" s="19" t="inlineStr">
+    <row r="59" ht="409" customHeight="1">
+      <c r="C59" s="19" t="inlineStr">
         <is>
           <t>{
   "data": [
     {
       "tanka_id": 1,
       "tanka_type": 1,
-      "tanka_type_label": "新聞購読料",
       "tanka_code": "T001",
       "tanka_name": "基本購読料（月額）",
+      "tekiyo_start_date": "2026-01-01",
+      "tekiyo_end_date": null,
       "kingaku_zeikomi": 4900,
       "kingaku_zeinuki": 4455,
-      "tax_rate": 10.00
+      "tax_rate": 10.00,
+      "active_flg": true,
+      "campaign_flg": false
     }
   ],
   "meta": {
@@ -5300,50 +5849,50 @@
 }</t>
         </is>
       </c>
-      <c r="D52" s="10" t="n"/>
-      <c r="E52" s="10" t="n"/>
-      <c r="F52" s="10" t="n"/>
-      <c r="G52" s="10" t="n"/>
-      <c r="H52" s="10" t="n"/>
-      <c r="I52" s="10" t="n"/>
-      <c r="J52" s="10" t="n"/>
-      <c r="K52" s="10" t="n"/>
-      <c r="L52" s="10" t="n"/>
-      <c r="M52" s="10" t="n"/>
-      <c r="N52" s="10" t="n"/>
-      <c r="O52" s="10" t="n"/>
-      <c r="P52" s="10" t="n"/>
-      <c r="Q52" s="10" t="n"/>
-      <c r="R52" s="10" t="n"/>
-      <c r="S52" s="10" t="n"/>
-      <c r="T52" s="10" t="n"/>
-      <c r="U52" s="10" t="n"/>
-      <c r="V52" s="10" t="n"/>
-      <c r="W52" s="10" t="n"/>
-      <c r="X52" s="10" t="n"/>
-      <c r="Y52" s="10" t="n"/>
-      <c r="Z52" s="10" t="n"/>
-      <c r="AA52" s="10" t="n"/>
-      <c r="AB52" s="10" t="n"/>
-      <c r="AC52" s="10" t="n"/>
-      <c r="AD52" s="10" t="n"/>
-      <c r="AE52" s="10" t="n"/>
-      <c r="AF52" s="10" t="n"/>
-      <c r="AG52" s="10" t="n"/>
-      <c r="AH52" s="10" t="n"/>
-      <c r="AI52" s="10" t="n"/>
-      <c r="AJ52" s="10" t="n"/>
-      <c r="AK52" s="11" t="n"/>
-    </row>
-    <row r="54" ht="19.5" customHeight="1">
-      <c r="B54" s="40" t="inlineStr">
+      <c r="D59" s="10" t="n"/>
+      <c r="E59" s="10" t="n"/>
+      <c r="F59" s="10" t="n"/>
+      <c r="G59" s="10" t="n"/>
+      <c r="H59" s="10" t="n"/>
+      <c r="I59" s="10" t="n"/>
+      <c r="J59" s="10" t="n"/>
+      <c r="K59" s="10" t="n"/>
+      <c r="L59" s="10" t="n"/>
+      <c r="M59" s="10" t="n"/>
+      <c r="N59" s="10" t="n"/>
+      <c r="O59" s="10" t="n"/>
+      <c r="P59" s="10" t="n"/>
+      <c r="Q59" s="10" t="n"/>
+      <c r="R59" s="10" t="n"/>
+      <c r="S59" s="10" t="n"/>
+      <c r="T59" s="10" t="n"/>
+      <c r="U59" s="10" t="n"/>
+      <c r="V59" s="10" t="n"/>
+      <c r="W59" s="10" t="n"/>
+      <c r="X59" s="10" t="n"/>
+      <c r="Y59" s="10" t="n"/>
+      <c r="Z59" s="10" t="n"/>
+      <c r="AA59" s="10" t="n"/>
+      <c r="AB59" s="10" t="n"/>
+      <c r="AC59" s="10" t="n"/>
+      <c r="AD59" s="10" t="n"/>
+      <c r="AE59" s="10" t="n"/>
+      <c r="AF59" s="10" t="n"/>
+      <c r="AG59" s="10" t="n"/>
+      <c r="AH59" s="10" t="n"/>
+      <c r="AI59" s="10" t="n"/>
+      <c r="AJ59" s="10" t="n"/>
+      <c r="AK59" s="11" t="n"/>
+    </row>
+    <row r="61" ht="19.5" customHeight="1">
+      <c r="B61" s="40" t="inlineStr">
         <is>
           <t>レスポンス（失敗 400 Bad Request）</t>
         </is>
       </c>
     </row>
-    <row r="55" ht="72" customHeight="1">
-      <c r="C55" s="19" t="inlineStr">
+    <row r="62" ht="72" customHeight="1">
+      <c r="C62" s="19" t="inlineStr">
         <is>
           <t>{
   "error_code": "BAD_REQUEST",
@@ -5351,50 +5900,50 @@
 }</t>
         </is>
       </c>
-      <c r="D55" s="10" t="n"/>
-      <c r="E55" s="10" t="n"/>
-      <c r="F55" s="10" t="n"/>
-      <c r="G55" s="10" t="n"/>
-      <c r="H55" s="10" t="n"/>
-      <c r="I55" s="10" t="n"/>
-      <c r="J55" s="10" t="n"/>
-      <c r="K55" s="10" t="n"/>
-      <c r="L55" s="10" t="n"/>
-      <c r="M55" s="10" t="n"/>
-      <c r="N55" s="10" t="n"/>
-      <c r="O55" s="10" t="n"/>
-      <c r="P55" s="10" t="n"/>
-      <c r="Q55" s="10" t="n"/>
-      <c r="R55" s="10" t="n"/>
-      <c r="S55" s="10" t="n"/>
-      <c r="T55" s="10" t="n"/>
-      <c r="U55" s="10" t="n"/>
-      <c r="V55" s="10" t="n"/>
-      <c r="W55" s="10" t="n"/>
-      <c r="X55" s="10" t="n"/>
-      <c r="Y55" s="10" t="n"/>
-      <c r="Z55" s="10" t="n"/>
-      <c r="AA55" s="10" t="n"/>
-      <c r="AB55" s="10" t="n"/>
-      <c r="AC55" s="10" t="n"/>
-      <c r="AD55" s="10" t="n"/>
-      <c r="AE55" s="10" t="n"/>
-      <c r="AF55" s="10" t="n"/>
-      <c r="AG55" s="10" t="n"/>
-      <c r="AH55" s="10" t="n"/>
-      <c r="AI55" s="10" t="n"/>
-      <c r="AJ55" s="10" t="n"/>
-      <c r="AK55" s="11" t="n"/>
-    </row>
-    <row r="57" ht="19.5" customHeight="1">
-      <c r="B57" s="40" t="inlineStr">
+      <c r="D62" s="10" t="n"/>
+      <c r="E62" s="10" t="n"/>
+      <c r="F62" s="10" t="n"/>
+      <c r="G62" s="10" t="n"/>
+      <c r="H62" s="10" t="n"/>
+      <c r="I62" s="10" t="n"/>
+      <c r="J62" s="10" t="n"/>
+      <c r="K62" s="10" t="n"/>
+      <c r="L62" s="10" t="n"/>
+      <c r="M62" s="10" t="n"/>
+      <c r="N62" s="10" t="n"/>
+      <c r="O62" s="10" t="n"/>
+      <c r="P62" s="10" t="n"/>
+      <c r="Q62" s="10" t="n"/>
+      <c r="R62" s="10" t="n"/>
+      <c r="S62" s="10" t="n"/>
+      <c r="T62" s="10" t="n"/>
+      <c r="U62" s="10" t="n"/>
+      <c r="V62" s="10" t="n"/>
+      <c r="W62" s="10" t="n"/>
+      <c r="X62" s="10" t="n"/>
+      <c r="Y62" s="10" t="n"/>
+      <c r="Z62" s="10" t="n"/>
+      <c r="AA62" s="10" t="n"/>
+      <c r="AB62" s="10" t="n"/>
+      <c r="AC62" s="10" t="n"/>
+      <c r="AD62" s="10" t="n"/>
+      <c r="AE62" s="10" t="n"/>
+      <c r="AF62" s="10" t="n"/>
+      <c r="AG62" s="10" t="n"/>
+      <c r="AH62" s="10" t="n"/>
+      <c r="AI62" s="10" t="n"/>
+      <c r="AJ62" s="10" t="n"/>
+      <c r="AK62" s="11" t="n"/>
+    </row>
+    <row r="64" ht="19.5" customHeight="1">
+      <c r="B64" s="40" t="inlineStr">
         <is>
           <t>レスポンス（失敗 401 Unauthorized）</t>
         </is>
       </c>
     </row>
-    <row r="58" ht="72" customHeight="1">
-      <c r="C58" s="19" t="inlineStr">
+    <row r="65" ht="72" customHeight="1">
+      <c r="C65" s="19" t="inlineStr">
         <is>
           <t>{
   "error_code": "UNAUTHORIZED",
@@ -5402,50 +5951,50 @@
 }</t>
         </is>
       </c>
-      <c r="D58" s="10" t="n"/>
-      <c r="E58" s="10" t="n"/>
-      <c r="F58" s="10" t="n"/>
-      <c r="G58" s="10" t="n"/>
-      <c r="H58" s="10" t="n"/>
-      <c r="I58" s="10" t="n"/>
-      <c r="J58" s="10" t="n"/>
-      <c r="K58" s="10" t="n"/>
-      <c r="L58" s="10" t="n"/>
-      <c r="M58" s="10" t="n"/>
-      <c r="N58" s="10" t="n"/>
-      <c r="O58" s="10" t="n"/>
-      <c r="P58" s="10" t="n"/>
-      <c r="Q58" s="10" t="n"/>
-      <c r="R58" s="10" t="n"/>
-      <c r="S58" s="10" t="n"/>
-      <c r="T58" s="10" t="n"/>
-      <c r="U58" s="10" t="n"/>
-      <c r="V58" s="10" t="n"/>
-      <c r="W58" s="10" t="n"/>
-      <c r="X58" s="10" t="n"/>
-      <c r="Y58" s="10" t="n"/>
-      <c r="Z58" s="10" t="n"/>
-      <c r="AA58" s="10" t="n"/>
-      <c r="AB58" s="10" t="n"/>
-      <c r="AC58" s="10" t="n"/>
-      <c r="AD58" s="10" t="n"/>
-      <c r="AE58" s="10" t="n"/>
-      <c r="AF58" s="10" t="n"/>
-      <c r="AG58" s="10" t="n"/>
-      <c r="AH58" s="10" t="n"/>
-      <c r="AI58" s="10" t="n"/>
-      <c r="AJ58" s="10" t="n"/>
-      <c r="AK58" s="11" t="n"/>
-    </row>
-    <row r="60" ht="19.5" customHeight="1">
-      <c r="B60" s="40" t="inlineStr">
+      <c r="D65" s="10" t="n"/>
+      <c r="E65" s="10" t="n"/>
+      <c r="F65" s="10" t="n"/>
+      <c r="G65" s="10" t="n"/>
+      <c r="H65" s="10" t="n"/>
+      <c r="I65" s="10" t="n"/>
+      <c r="J65" s="10" t="n"/>
+      <c r="K65" s="10" t="n"/>
+      <c r="L65" s="10" t="n"/>
+      <c r="M65" s="10" t="n"/>
+      <c r="N65" s="10" t="n"/>
+      <c r="O65" s="10" t="n"/>
+      <c r="P65" s="10" t="n"/>
+      <c r="Q65" s="10" t="n"/>
+      <c r="R65" s="10" t="n"/>
+      <c r="S65" s="10" t="n"/>
+      <c r="T65" s="10" t="n"/>
+      <c r="U65" s="10" t="n"/>
+      <c r="V65" s="10" t="n"/>
+      <c r="W65" s="10" t="n"/>
+      <c r="X65" s="10" t="n"/>
+      <c r="Y65" s="10" t="n"/>
+      <c r="Z65" s="10" t="n"/>
+      <c r="AA65" s="10" t="n"/>
+      <c r="AB65" s="10" t="n"/>
+      <c r="AC65" s="10" t="n"/>
+      <c r="AD65" s="10" t="n"/>
+      <c r="AE65" s="10" t="n"/>
+      <c r="AF65" s="10" t="n"/>
+      <c r="AG65" s="10" t="n"/>
+      <c r="AH65" s="10" t="n"/>
+      <c r="AI65" s="10" t="n"/>
+      <c r="AJ65" s="10" t="n"/>
+      <c r="AK65" s="11" t="n"/>
+    </row>
+    <row r="67" ht="19.5" customHeight="1">
+      <c r="B67" s="40" t="inlineStr">
         <is>
           <t>レスポンス（失敗 403 Forbidden）</t>
         </is>
       </c>
     </row>
-    <row r="61" ht="72" customHeight="1">
-      <c r="C61" s="19" t="inlineStr">
+    <row r="68" ht="72" customHeight="1">
+      <c r="C68" s="19" t="inlineStr">
         <is>
           <t>{
   "error_code": "FORBIDDEN",
@@ -5453,50 +6002,50 @@
 }</t>
         </is>
       </c>
-      <c r="D61" s="10" t="n"/>
-      <c r="E61" s="10" t="n"/>
-      <c r="F61" s="10" t="n"/>
-      <c r="G61" s="10" t="n"/>
-      <c r="H61" s="10" t="n"/>
-      <c r="I61" s="10" t="n"/>
-      <c r="J61" s="10" t="n"/>
-      <c r="K61" s="10" t="n"/>
-      <c r="L61" s="10" t="n"/>
-      <c r="M61" s="10" t="n"/>
-      <c r="N61" s="10" t="n"/>
-      <c r="O61" s="10" t="n"/>
-      <c r="P61" s="10" t="n"/>
-      <c r="Q61" s="10" t="n"/>
-      <c r="R61" s="10" t="n"/>
-      <c r="S61" s="10" t="n"/>
-      <c r="T61" s="10" t="n"/>
-      <c r="U61" s="10" t="n"/>
-      <c r="V61" s="10" t="n"/>
-      <c r="W61" s="10" t="n"/>
-      <c r="X61" s="10" t="n"/>
-      <c r="Y61" s="10" t="n"/>
-      <c r="Z61" s="10" t="n"/>
-      <c r="AA61" s="10" t="n"/>
-      <c r="AB61" s="10" t="n"/>
-      <c r="AC61" s="10" t="n"/>
-      <c r="AD61" s="10" t="n"/>
-      <c r="AE61" s="10" t="n"/>
-      <c r="AF61" s="10" t="n"/>
-      <c r="AG61" s="10" t="n"/>
-      <c r="AH61" s="10" t="n"/>
-      <c r="AI61" s="10" t="n"/>
-      <c r="AJ61" s="10" t="n"/>
-      <c r="AK61" s="11" t="n"/>
-    </row>
-    <row r="63" ht="19.5" customHeight="1">
-      <c r="B63" s="40" t="inlineStr">
+      <c r="D68" s="10" t="n"/>
+      <c r="E68" s="10" t="n"/>
+      <c r="F68" s="10" t="n"/>
+      <c r="G68" s="10" t="n"/>
+      <c r="H68" s="10" t="n"/>
+      <c r="I68" s="10" t="n"/>
+      <c r="J68" s="10" t="n"/>
+      <c r="K68" s="10" t="n"/>
+      <c r="L68" s="10" t="n"/>
+      <c r="M68" s="10" t="n"/>
+      <c r="N68" s="10" t="n"/>
+      <c r="O68" s="10" t="n"/>
+      <c r="P68" s="10" t="n"/>
+      <c r="Q68" s="10" t="n"/>
+      <c r="R68" s="10" t="n"/>
+      <c r="S68" s="10" t="n"/>
+      <c r="T68" s="10" t="n"/>
+      <c r="U68" s="10" t="n"/>
+      <c r="V68" s="10" t="n"/>
+      <c r="W68" s="10" t="n"/>
+      <c r="X68" s="10" t="n"/>
+      <c r="Y68" s="10" t="n"/>
+      <c r="Z68" s="10" t="n"/>
+      <c r="AA68" s="10" t="n"/>
+      <c r="AB68" s="10" t="n"/>
+      <c r="AC68" s="10" t="n"/>
+      <c r="AD68" s="10" t="n"/>
+      <c r="AE68" s="10" t="n"/>
+      <c r="AF68" s="10" t="n"/>
+      <c r="AG68" s="10" t="n"/>
+      <c r="AH68" s="10" t="n"/>
+      <c r="AI68" s="10" t="n"/>
+      <c r="AJ68" s="10" t="n"/>
+      <c r="AK68" s="11" t="n"/>
+    </row>
+    <row r="70" ht="19.5" customHeight="1">
+      <c r="B70" s="40" t="inlineStr">
         <is>
           <t>レスポンス（失敗 500 Internal Server Error）</t>
         </is>
       </c>
     </row>
-    <row r="64" ht="72" customHeight="1">
-      <c r="C64" s="19" t="inlineStr">
+    <row r="71" ht="72" customHeight="1">
+      <c r="C71" s="19" t="inlineStr">
         <is>
           <t>{
   "error_code": "INTERNAL_SERVER_ERROR",
@@ -5504,552 +6053,620 @@
 }</t>
         </is>
       </c>
-      <c r="D64" s="10" t="n"/>
-      <c r="E64" s="10" t="n"/>
-      <c r="F64" s="10" t="n"/>
-      <c r="G64" s="10" t="n"/>
-      <c r="H64" s="10" t="n"/>
-      <c r="I64" s="10" t="n"/>
-      <c r="J64" s="10" t="n"/>
-      <c r="K64" s="10" t="n"/>
-      <c r="L64" s="10" t="n"/>
-      <c r="M64" s="10" t="n"/>
-      <c r="N64" s="10" t="n"/>
-      <c r="O64" s="10" t="n"/>
-      <c r="P64" s="10" t="n"/>
-      <c r="Q64" s="10" t="n"/>
-      <c r="R64" s="10" t="n"/>
-      <c r="S64" s="10" t="n"/>
-      <c r="T64" s="10" t="n"/>
-      <c r="U64" s="10" t="n"/>
-      <c r="V64" s="10" t="n"/>
-      <c r="W64" s="10" t="n"/>
-      <c r="X64" s="10" t="n"/>
-      <c r="Y64" s="10" t="n"/>
-      <c r="Z64" s="10" t="n"/>
-      <c r="AA64" s="10" t="n"/>
-      <c r="AB64" s="10" t="n"/>
-      <c r="AC64" s="10" t="n"/>
-      <c r="AD64" s="10" t="n"/>
-      <c r="AE64" s="10" t="n"/>
-      <c r="AF64" s="10" t="n"/>
-      <c r="AG64" s="10" t="n"/>
-      <c r="AH64" s="10" t="n"/>
-      <c r="AI64" s="10" t="n"/>
-      <c r="AJ64" s="10" t="n"/>
-      <c r="AK64" s="11" t="n"/>
-    </row>
-    <row r="66" ht="19.5" customHeight="1"/>
-    <row r="67" ht="19.5" customHeight="1">
-      <c r="A67" s="27" t="inlineStr">
+      <c r="D71" s="10" t="n"/>
+      <c r="E71" s="10" t="n"/>
+      <c r="F71" s="10" t="n"/>
+      <c r="G71" s="10" t="n"/>
+      <c r="H71" s="10" t="n"/>
+      <c r="I71" s="10" t="n"/>
+      <c r="J71" s="10" t="n"/>
+      <c r="K71" s="10" t="n"/>
+      <c r="L71" s="10" t="n"/>
+      <c r="M71" s="10" t="n"/>
+      <c r="N71" s="10" t="n"/>
+      <c r="O71" s="10" t="n"/>
+      <c r="P71" s="10" t="n"/>
+      <c r="Q71" s="10" t="n"/>
+      <c r="R71" s="10" t="n"/>
+      <c r="S71" s="10" t="n"/>
+      <c r="T71" s="10" t="n"/>
+      <c r="U71" s="10" t="n"/>
+      <c r="V71" s="10" t="n"/>
+      <c r="W71" s="10" t="n"/>
+      <c r="X71" s="10" t="n"/>
+      <c r="Y71" s="10" t="n"/>
+      <c r="Z71" s="10" t="n"/>
+      <c r="AA71" s="10" t="n"/>
+      <c r="AB71" s="10" t="n"/>
+      <c r="AC71" s="10" t="n"/>
+      <c r="AD71" s="10" t="n"/>
+      <c r="AE71" s="10" t="n"/>
+      <c r="AF71" s="10" t="n"/>
+      <c r="AG71" s="10" t="n"/>
+      <c r="AH71" s="10" t="n"/>
+      <c r="AI71" s="10" t="n"/>
+      <c r="AJ71" s="10" t="n"/>
+      <c r="AK71" s="11" t="n"/>
+    </row>
+    <row r="73" ht="19.5" customHeight="1"/>
+    <row r="74" ht="19.5" customHeight="1">
+      <c r="A74" s="27" t="inlineStr">
         <is>
           <t>4. 処理手順</t>
         </is>
       </c>
     </row>
-    <row r="68" ht="18" customHeight="1">
-      <c r="B68" s="27" t="inlineStr">
+    <row r="75" ht="18" customHeight="1">
+      <c r="B75" s="27" t="inlineStr">
         <is>
           <t>4.1 リクエストのバリデーション</t>
-        </is>
-      </c>
-    </row>
-    <row r="69" ht="18" customHeight="1">
-      <c r="C69" s="41" t="inlineStr">
-        <is>
-          <t>クエリパラメータの検証：</t>
-        </is>
-      </c>
-    </row>
-    <row r="70" ht="18" customHeight="1">
-      <c r="D70" s="41" t="inlineStr">
-        <is>
-          <t>型チェック（string / number / enum）</t>
-        </is>
-      </c>
-    </row>
-    <row r="71" ht="18" customHeight="1">
-      <c r="D71" s="41" t="inlineStr">
-        <is>
-          <t>最大・最小値チェック</t>
-        </is>
-      </c>
-    </row>
-    <row r="72" ht="18" customHeight="1">
-      <c r="D72" s="41" t="inlineStr">
-        <is>
-          <t>必須項目チェック（該当する場合）</t>
-        </is>
-      </c>
-    </row>
-    <row r="73" ht="18" customHeight="1">
-      <c r="C73" s="41" t="inlineStr">
-        <is>
-          <t>デフォルト値の適用：</t>
-        </is>
-      </c>
-    </row>
-    <row r="74" ht="18" customHeight="1">
-      <c r="D74" s="41" t="inlineStr">
-        <is>
-          <t>page：未指定の場合、1</t>
-        </is>
-      </c>
-    </row>
-    <row r="75" ht="18" customHeight="1">
-      <c r="D75" s="41" t="inlineStr">
-        <is>
-          <t>per_page：未指定の場合、20</t>
         </is>
       </c>
     </row>
     <row r="76" ht="18" customHeight="1">
       <c r="C76" s="41" t="inlineStr">
         <is>
-          <t>不正なパラメータが存在する場合：</t>
+          <t>クエリパラメータの検証：</t>
         </is>
       </c>
     </row>
     <row r="77" ht="18" customHeight="1">
       <c r="D77" s="41" t="inlineStr">
         <is>
-          <t>HTTP 400 Bad Request を返却する。</t>
+          <t>型チェック（string / number / enum）</t>
         </is>
       </c>
     </row>
     <row r="78" ht="18" customHeight="1">
-      <c r="B78" s="27" t="inlineStr">
-        <is>
-          <t>4.2 認証・認可チェック</t>
+      <c r="D78" s="41" t="inlineStr">
+        <is>
+          <t>最大・最小値チェック</t>
         </is>
       </c>
     </row>
     <row r="79" ht="18" customHeight="1">
-      <c r="C79" s="41" t="inlineStr">
-        <is>
-          <t>認証情報を検証する（JWT / Cookie）。</t>
+      <c r="D79" s="41" t="inlineStr">
+        <is>
+          <t>必須項目チェック（該当する場合）</t>
         </is>
       </c>
     </row>
     <row r="80" ht="18" customHeight="1">
       <c r="C80" s="41" t="inlineStr">
         <is>
-          <t>認証失敗の場合：HTTP 401 Unauthorized</t>
+          <t>デフォルト値の適用：</t>
         </is>
       </c>
     </row>
     <row r="81" ht="18" customHeight="1">
-      <c r="C81" s="41" t="inlineStr">
-        <is>
-          <t>権限チェック：tanka.view を保持しているか確認する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="82" ht="36" customHeight="1">
+      <c r="D81" s="41" t="inlineStr">
+        <is>
+          <t>page：未指定の場合、1</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="18" customHeight="1">
       <c r="D82" s="41" t="inlineStr">
         <is>
-          <t>対象ロール：CHUOKAI（中央会）, JA_HONTEN（JA本店）, JA_KANRI_SHITEN（JA管理支店）</t>
+          <t>per_page：未指定の場合、20</t>
         </is>
       </c>
     </row>
     <row r="83" ht="18" customHeight="1">
       <c r="C83" s="41" t="inlineStr">
         <is>
-          <t>権限がない場合：HTTP 403 Forbidden</t>
+          <t>不正なパラメータが存在する場合：</t>
         </is>
       </c>
     </row>
     <row r="84" ht="18" customHeight="1">
-      <c r="B84" s="27" t="inlineStr">
-        <is>
-          <t>4.3 データ取得条件の設定</t>
+      <c r="D84" s="41" t="inlineStr">
+        <is>
+          <t>HTTP 400 Bad Request を返却する。</t>
         </is>
       </c>
     </row>
     <row r="85" ht="18" customHeight="1">
-      <c r="C85" s="41" t="inlineStr">
-        <is>
-          <t>ログインユーザーのスコープを取得する（例：ja_id）。</t>
+      <c r="B85" s="27" t="inlineStr">
+        <is>
+          <t>4.2 認証・認可チェック</t>
         </is>
       </c>
     </row>
     <row r="86" ht="18" customHeight="1">
       <c r="C86" s="41" t="inlineStr">
         <is>
-          <t>基本条件：</t>
+          <t>認証情報を検証する（HTTP-only Cookieセッション）。</t>
         </is>
       </c>
     </row>
     <row r="87" ht="18" customHeight="1">
-      <c r="D87" s="41" t="inlineStr">
-        <is>
-          <t>スコープ制御（ja_id = user.ja_id）</t>
+      <c r="C87" s="41" t="inlineStr">
+        <is>
+          <t>認証失敗の場合：HTTP 401 Unauthorized</t>
         </is>
       </c>
     </row>
     <row r="88" ht="18" customHeight="1">
-      <c r="D88" s="41" t="inlineStr">
-        <is>
-          <t>論理削除除外（deleted_at IS NULL）</t>
+      <c r="C88" s="41" t="inlineStr">
+        <is>
+          <t>権限チェック：tanka.view を保持しているか確認する。</t>
         </is>
       </c>
     </row>
     <row r="89" ht="36" customHeight="1">
       <c r="D89" s="41" t="inlineStr">
         <is>
-          <t>有効期間条件（tekiyo_end_date IS NULL OR tekiyo_end_date &gt;= CURRENT_DATE）</t>
+          <t>対象ロール：CHUOKAI（中央会）, JA_HONTEN（JA本店）, JA_KANRI_SHITEN（JA管理支店）</t>
         </is>
       </c>
     </row>
     <row r="90" ht="18" customHeight="1">
       <c r="C90" s="41" t="inlineStr">
         <is>
+          <t>権限がない場合：HTTP 403 Forbidden</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="18" customHeight="1">
+      <c r="B91" s="27" t="inlineStr">
+        <is>
+          <t>4.3 データ取得条件の設定</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="18" customHeight="1">
+      <c r="C92" s="41" t="inlineStr">
+        <is>
+          <t>ログインユーザーのスコープを取得する（例：ja_id）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="18" customHeight="1">
+      <c r="C93" s="41" t="inlineStr">
+        <is>
+          <t>基本条件：</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="18" customHeight="1">
+      <c r="D94" s="41" t="inlineStr">
+        <is>
+          <t>スコープ制御（ja_id = user.ja_id）</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="18" customHeight="1">
+      <c r="D95" s="41" t="inlineStr">
+        <is>
+          <t>論理削除除外（deleted_at IS NULL）</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="18" customHeight="1">
+      <c r="D96" s="41" t="inlineStr">
+        <is>
+          <t>※ 顧客要件（2026-06）：既定の有効期間条件</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="18" customHeight="1">
+      <c r="C97" s="41" t="inlineStr">
+        <is>
           <t>検索条件：</t>
         </is>
       </c>
     </row>
-    <row r="91" ht="18" customHeight="1">
-      <c r="D91" s="41" t="inlineStr">
+    <row r="98" ht="18" customHeight="1">
+      <c r="D98" s="41" t="inlineStr">
         <is>
           <t>tanka_type：完全一致（=）</t>
         </is>
       </c>
     </row>
-    <row r="92" ht="18" customHeight="1">
-      <c r="D92" s="41" t="inlineStr">
+    <row r="99" ht="18" customHeight="1">
+      <c r="D99" s="41" t="inlineStr">
         <is>
           <t>tanka_name：部分一致（ILIKE '%value%'）</t>
         </is>
       </c>
     </row>
-    <row r="93" ht="18" customHeight="1">
-      <c r="D93" s="41" t="inlineStr">
+    <row r="100" ht="36" customHeight="1">
+      <c r="D100" s="41" t="inlineStr">
+        <is>
+          <t>tekiyo_start_date：`tekiyo_start_date &gt;= :tekiyo_start_date`（指定日以降に開始するレコード）。省略時は条件適用なし</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="54" customHeight="1">
+      <c r="D101" s="41" t="inlineStr">
+        <is>
+          <t>tekiyo_end_date：`tekiyo_end_date IS NOT NULL AND tekiyo_end_date &lt;= :tekiyo_end_date`（指定日以前に終了するレコード）。NULL（無期限）は対象外。省略時は条件適用なし</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" ht="18" customHeight="1">
+      <c r="D102" s="41" t="inlineStr">
+        <is>
+          <t>active_flg：完全一致（指定された場合のみ）。省略時は両方（有効中・停止中）を返却</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" ht="18" customHeight="1">
+      <c r="D103" s="41" t="inlineStr">
+        <is>
+          <t>campaign_flg：完全一致（指定された場合のみ）。省略時は両方（有効・無効）を返却</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="18" customHeight="1">
+      <c r="D104" s="41" t="inlineStr">
         <is>
           <t>sort_by / sort_order：ソート適用</t>
         </is>
       </c>
     </row>
-    <row r="94" ht="18" customHeight="1">
-      <c r="B94" s="27" t="inlineStr">
+    <row r="105" ht="18" customHeight="1">
+      <c r="B105" s="27" t="inlineStr">
         <is>
           <t>4.4 データ件数の取得</t>
         </is>
       </c>
     </row>
-    <row r="95" ht="18" customHeight="1">
-      <c r="C95" s="41" t="inlineStr">
+    <row r="106" ht="18" customHeight="1">
+      <c r="C106" s="41" t="inlineStr">
         <is>
           <t>条件に一致する総件数を取得する。</t>
         </is>
       </c>
     </row>
-    <row r="96" ht="18" customHeight="1">
-      <c r="C96" s="41" t="inlineStr">
+    <row r="107" ht="18" customHeight="1">
+      <c r="C107" s="41" t="inlineStr">
         <is>
           <t>meta.total に使用する</t>
         </is>
       </c>
     </row>
-    <row r="97" ht="18" customHeight="1">
-      <c r="B97" s="27" t="inlineStr">
+    <row r="108" ht="18" customHeight="1">
+      <c r="B108" s="27" t="inlineStr">
         <is>
           <t>4.5 ソート・ページング</t>
         </is>
       </c>
     </row>
-    <row r="98" ht="18" customHeight="1">
-      <c r="C98" s="41" t="inlineStr">
+    <row r="109" ht="18" customHeight="1">
+      <c r="C109" s="41" t="inlineStr">
         <is>
           <t>sort_by / sort_order でソート適用。</t>
         </is>
       </c>
     </row>
-    <row r="99" ht="18" customHeight="1">
-      <c r="C99" s="41" t="inlineStr">
+    <row r="110" ht="18" customHeight="1">
+      <c r="C110" s="41" t="inlineStr">
         <is>
           <t>OFFSET = (page - 1) * per_page, LIMIT = per_page</t>
         </is>
       </c>
     </row>
-    <row r="100" ht="18" customHeight="1">
-      <c r="B100" s="27" t="inlineStr">
+    <row r="111" ht="18" customHeight="1">
+      <c r="B111" s="27" t="inlineStr">
         <is>
           <t>4.6 データ取得</t>
         </is>
       </c>
     </row>
-    <row r="101" ht="18" customHeight="1">
-      <c r="C101" s="41" t="inlineStr">
+    <row r="112" ht="18" customHeight="1">
+      <c r="C112" s="41" t="inlineStr">
         <is>
           <t>以下のSQLを実行してデータを取得する。</t>
         </is>
       </c>
     </row>
-    <row r="102" ht="198" customHeight="1">
-      <c r="C102" s="42" t="inlineStr">
+    <row r="113" ht="288" customHeight="1">
+      <c r="C113" s="42" t="inlineStr">
         <is>
           <t>SELECT tanka_id, tanka_type, tanka_code, tanka_name,
-       kingaku_zeikomi, kingaku_zeinuki, tax_rate
+       tekiyo_start_date, tekiyo_end_date,
+       kingaku_zeikomi, kingaku_zeinuki, tax_rate, active_flg, campaign_flg
 FROM m_tanka
 WHERE ja_id = :ja_id
   AND deleted_at IS NULL
-  AND (tekiyo_end_date IS NULL OR tekiyo_end_date &gt;= CURRENT_DATE)
+  -- 顧客要件(2026-06): 既定の有効期間条件は廃止（期限切れも全件表示）
   AND (:tanka_type IS NULL OR tanka_type = :tanka_type)
   AND (:tanka_name IS NULL OR tanka_name ILIKE '%' || :tanka_name || '%')
+  AND (:tekiyo_start_date IS NULL OR tekiyo_start_date &gt;= :tekiyo_start_date)
+  AND (:tekiyo_end_date IS NULL OR (tekiyo_end_date IS NOT NULL AND tekiyo_end_date &lt;= :tekiyo_end_date))
+  AND (:active_flg IS NULL OR active_flg = :active_flg)
+  AND (:campaign_flg IS NULL OR campaign_flg = :campaign_flg)
 ORDER BY {sort_by} {sort_order}
 LIMIT :per_page
 OFFSET (:page - 1) * :per_page</t>
         </is>
       </c>
-      <c r="D102" s="10" t="n"/>
-      <c r="E102" s="10" t="n"/>
-      <c r="F102" s="10" t="n"/>
-      <c r="G102" s="10" t="n"/>
-      <c r="H102" s="10" t="n"/>
-      <c r="I102" s="10" t="n"/>
-      <c r="J102" s="10" t="n"/>
-      <c r="K102" s="10" t="n"/>
-      <c r="L102" s="10" t="n"/>
-      <c r="M102" s="10" t="n"/>
-      <c r="N102" s="10" t="n"/>
-      <c r="O102" s="10" t="n"/>
-      <c r="P102" s="10" t="n"/>
-      <c r="Q102" s="10" t="n"/>
-      <c r="R102" s="10" t="n"/>
-      <c r="S102" s="10" t="n"/>
-      <c r="T102" s="10" t="n"/>
-      <c r="U102" s="10" t="n"/>
-      <c r="V102" s="10" t="n"/>
-      <c r="W102" s="10" t="n"/>
-      <c r="X102" s="10" t="n"/>
-      <c r="Y102" s="10" t="n"/>
-      <c r="Z102" s="10" t="n"/>
-      <c r="AA102" s="10" t="n"/>
-      <c r="AB102" s="10" t="n"/>
-      <c r="AC102" s="10" t="n"/>
-      <c r="AD102" s="10" t="n"/>
-      <c r="AE102" s="10" t="n"/>
-      <c r="AF102" s="10" t="n"/>
-      <c r="AG102" s="10" t="n"/>
-      <c r="AH102" s="10" t="n"/>
-      <c r="AI102" s="10" t="n"/>
-      <c r="AJ102" s="10" t="n"/>
-      <c r="AK102" s="11" t="n"/>
-    </row>
-    <row r="103" ht="18" customHeight="1">
-      <c r="C103" s="41" t="inlineStr">
-        <is>
-          <t>tanka_type 値をラベルにマッピング（1 → 新聞購読料, 2 → 配達手数料）</t>
-        </is>
-      </c>
-    </row>
-    <row r="104" ht="18" customHeight="1">
-      <c r="B104" s="27" t="inlineStr">
+      <c r="D113" s="10" t="n"/>
+      <c r="E113" s="10" t="n"/>
+      <c r="F113" s="10" t="n"/>
+      <c r="G113" s="10" t="n"/>
+      <c r="H113" s="10" t="n"/>
+      <c r="I113" s="10" t="n"/>
+      <c r="J113" s="10" t="n"/>
+      <c r="K113" s="10" t="n"/>
+      <c r="L113" s="10" t="n"/>
+      <c r="M113" s="10" t="n"/>
+      <c r="N113" s="10" t="n"/>
+      <c r="O113" s="10" t="n"/>
+      <c r="P113" s="10" t="n"/>
+      <c r="Q113" s="10" t="n"/>
+      <c r="R113" s="10" t="n"/>
+      <c r="S113" s="10" t="n"/>
+      <c r="T113" s="10" t="n"/>
+      <c r="U113" s="10" t="n"/>
+      <c r="V113" s="10" t="n"/>
+      <c r="W113" s="10" t="n"/>
+      <c r="X113" s="10" t="n"/>
+      <c r="Y113" s="10" t="n"/>
+      <c r="Z113" s="10" t="n"/>
+      <c r="AA113" s="10" t="n"/>
+      <c r="AB113" s="10" t="n"/>
+      <c r="AC113" s="10" t="n"/>
+      <c r="AD113" s="10" t="n"/>
+      <c r="AE113" s="10" t="n"/>
+      <c r="AF113" s="10" t="n"/>
+      <c r="AG113" s="10" t="n"/>
+      <c r="AH113" s="10" t="n"/>
+      <c r="AI113" s="10" t="n"/>
+      <c r="AJ113" s="10" t="n"/>
+      <c r="AK113" s="11" t="n"/>
+    </row>
+    <row r="114" ht="72" customHeight="1">
+      <c r="C114" s="41" t="inlineStr">
+        <is>
+          <t>tanka_type はコード値（1 または 2）のみを返却する。ラベル変換は行わない（`_label` フィールドは付与しない — FE 側で `useCodesStore().label('TANKA_TYPE', value)` により解決する。.claude/rules/nestjs.md §m_code 参照）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="115" ht="18" customHeight="1">
+      <c r="B115" s="27" t="inlineStr">
         <is>
           <t>4.7 レスポンス生成</t>
         </is>
       </c>
     </row>
-    <row r="105" ht="18" customHeight="1">
-      <c r="C105" s="41" t="inlineStr">
+    <row r="116" ht="18" customHeight="1">
+      <c r="C116" s="41" t="inlineStr">
         <is>
           <t>data 配列と meta オブジェクトを含むJSONを返却する。</t>
         </is>
       </c>
     </row>
-    <row r="106" ht="18" customHeight="1">
-      <c r="B106" s="27" t="inlineStr">
+    <row r="117" ht="18" customHeight="1">
+      <c r="B117" s="27" t="inlineStr">
         <is>
           <t>4.8 例外処理</t>
         </is>
       </c>
     </row>
-    <row r="107" ht="18" customHeight="1">
-      <c r="C107" s="41" t="inlineStr">
+    <row r="118" ht="18" customHeight="1">
+      <c r="C118" s="41" t="inlineStr">
         <is>
           <t>DB接続エラー等の場合：HTTP 500 Internal Server Error を返却する。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="236">
+  <mergeCells count="286">
     <mergeCell ref="J11:AK11"/>
     <mergeCell ref="Y28:AB28"/>
+    <mergeCell ref="Q29:S29"/>
+    <mergeCell ref="Y49:AE49"/>
     <mergeCell ref="C23:L23"/>
     <mergeCell ref="Q23:S23"/>
+    <mergeCell ref="D78:AK78"/>
     <mergeCell ref="Y36:AE36"/>
     <mergeCell ref="T24:X24"/>
-    <mergeCell ref="D87:AK87"/>
-    <mergeCell ref="C34:C41"/>
     <mergeCell ref="Y45:AE45"/>
-    <mergeCell ref="T33:X33"/>
     <mergeCell ref="AC23:AE23"/>
-    <mergeCell ref="B54:I54"/>
-    <mergeCell ref="C102:AK102"/>
-    <mergeCell ref="D71:AK71"/>
+    <mergeCell ref="D48:L48"/>
+    <mergeCell ref="Q31:S31"/>
     <mergeCell ref="M32:P32"/>
     <mergeCell ref="N18:AK18"/>
-    <mergeCell ref="C86:AK86"/>
+    <mergeCell ref="M29:P29"/>
     <mergeCell ref="J18:M18"/>
     <mergeCell ref="M23:P23"/>
+    <mergeCell ref="C68:AK68"/>
+    <mergeCell ref="C86:AK86"/>
+    <mergeCell ref="Y32:AB32"/>
+    <mergeCell ref="T53:X53"/>
     <mergeCell ref="J12:AK12"/>
     <mergeCell ref="M46:P46"/>
-    <mergeCell ref="B48:I48"/>
-    <mergeCell ref="C58:AK58"/>
+    <mergeCell ref="B70:I70"/>
     <mergeCell ref="N17:AK17"/>
     <mergeCell ref="J17:M17"/>
+    <mergeCell ref="C49:L49"/>
     <mergeCell ref="D82:AK82"/>
     <mergeCell ref="M43:P43"/>
+    <mergeCell ref="Y52:AE52"/>
     <mergeCell ref="AF23:AK23"/>
-    <mergeCell ref="C42:L42"/>
+    <mergeCell ref="AF50:AK50"/>
+    <mergeCell ref="C113:AK113"/>
     <mergeCell ref="B8:I8"/>
-    <mergeCell ref="C85:AK85"/>
+    <mergeCell ref="C112:AK112"/>
     <mergeCell ref="J1:P1"/>
     <mergeCell ref="AH2:AK3"/>
     <mergeCell ref="Y24:AB24"/>
+    <mergeCell ref="A34:AK34"/>
+    <mergeCell ref="C65:AK65"/>
+    <mergeCell ref="C109:AK109"/>
     <mergeCell ref="Q41:S41"/>
+    <mergeCell ref="D42:L42"/>
+    <mergeCell ref="D51:L51"/>
+    <mergeCell ref="AF52:AK52"/>
     <mergeCell ref="Q1:U1"/>
+    <mergeCell ref="D99:AK99"/>
     <mergeCell ref="B10:I10"/>
-    <mergeCell ref="M35:P35"/>
+    <mergeCell ref="C80:AK80"/>
     <mergeCell ref="AF22:AK22"/>
-    <mergeCell ref="C80:AK80"/>
+    <mergeCell ref="C38:C48"/>
+    <mergeCell ref="C114:AK114"/>
     <mergeCell ref="AF36:AK36"/>
     <mergeCell ref="Q25:S25"/>
-    <mergeCell ref="D35:L35"/>
     <mergeCell ref="Q43:S43"/>
     <mergeCell ref="J2:P3"/>
     <mergeCell ref="T22:X22"/>
     <mergeCell ref="B9:I9"/>
-    <mergeCell ref="AF34:AK34"/>
-    <mergeCell ref="C95:AK95"/>
-    <mergeCell ref="D34:L34"/>
+    <mergeCell ref="T31:X31"/>
+    <mergeCell ref="D101:AK101"/>
     <mergeCell ref="C22:L22"/>
-    <mergeCell ref="Q33:S33"/>
     <mergeCell ref="D77:AK77"/>
-    <mergeCell ref="T34:X34"/>
     <mergeCell ref="Q42:S42"/>
     <mergeCell ref="M25:P25"/>
     <mergeCell ref="T28:X28"/>
     <mergeCell ref="Y40:AE40"/>
+    <mergeCell ref="AF49:AK49"/>
+    <mergeCell ref="B91:AK91"/>
     <mergeCell ref="T37:X37"/>
+    <mergeCell ref="C106:AK106"/>
     <mergeCell ref="Y25:AB25"/>
-    <mergeCell ref="D36:L36"/>
-    <mergeCell ref="D75:AK75"/>
-    <mergeCell ref="M33:P33"/>
     <mergeCell ref="M45:P45"/>
-    <mergeCell ref="D72:AK72"/>
+    <mergeCell ref="B115:AK115"/>
+    <mergeCell ref="T30:X30"/>
+    <mergeCell ref="D103:AK103"/>
+    <mergeCell ref="T29:X29"/>
     <mergeCell ref="AF44:AK44"/>
     <mergeCell ref="T38:X38"/>
-    <mergeCell ref="C49:AK49"/>
+    <mergeCell ref="M47:P47"/>
+    <mergeCell ref="B117:AK117"/>
     <mergeCell ref="C32:L32"/>
     <mergeCell ref="Z1:AC1"/>
-    <mergeCell ref="C101:AK101"/>
+    <mergeCell ref="D53:L53"/>
     <mergeCell ref="N14:AK14"/>
-    <mergeCell ref="Y33:AE33"/>
+    <mergeCell ref="D47:L47"/>
+    <mergeCell ref="AC29:AE29"/>
     <mergeCell ref="B12:I12"/>
     <mergeCell ref="Q44:S44"/>
     <mergeCell ref="Q22:S22"/>
-    <mergeCell ref="D37:L37"/>
     <mergeCell ref="Q46:S46"/>
+    <mergeCell ref="AF51:AK51"/>
     <mergeCell ref="AC22:AE22"/>
+    <mergeCell ref="C88:AK88"/>
+    <mergeCell ref="Y53:AE53"/>
     <mergeCell ref="D89:AK89"/>
+    <mergeCell ref="AC31:AE31"/>
     <mergeCell ref="AF32:AK32"/>
-    <mergeCell ref="B78:AK78"/>
+    <mergeCell ref="D98:AK98"/>
     <mergeCell ref="Z2:AC3"/>
     <mergeCell ref="AF26:AK26"/>
     <mergeCell ref="AF41:AK41"/>
     <mergeCell ref="C24:L24"/>
-    <mergeCell ref="AF35:AK35"/>
     <mergeCell ref="D39:L39"/>
+    <mergeCell ref="M44:P44"/>
     <mergeCell ref="AD2:AG3"/>
-    <mergeCell ref="C33:L33"/>
-    <mergeCell ref="M44:P44"/>
+    <mergeCell ref="D79:AK79"/>
+    <mergeCell ref="Q48:S48"/>
     <mergeCell ref="B14:I18"/>
-    <mergeCell ref="A67:AK67"/>
     <mergeCell ref="B13:I13"/>
-    <mergeCell ref="D88:AK88"/>
-    <mergeCell ref="C103:AK103"/>
     <mergeCell ref="Q45:S45"/>
     <mergeCell ref="AF38:AK38"/>
-    <mergeCell ref="C55:AK55"/>
-    <mergeCell ref="C99:AK99"/>
     <mergeCell ref="Q32:S32"/>
     <mergeCell ref="D38:L38"/>
     <mergeCell ref="T40:X40"/>
     <mergeCell ref="C26:L26"/>
+    <mergeCell ref="D81:AK81"/>
     <mergeCell ref="Y39:AE39"/>
+    <mergeCell ref="C118:AK118"/>
+    <mergeCell ref="M51:P51"/>
     <mergeCell ref="J13:AK13"/>
     <mergeCell ref="AF27:AK27"/>
-    <mergeCell ref="B104:AK104"/>
+    <mergeCell ref="Q47:S47"/>
+    <mergeCell ref="C59:AK59"/>
     <mergeCell ref="C25:L25"/>
     <mergeCell ref="AF37:AK37"/>
     <mergeCell ref="A2:I3"/>
     <mergeCell ref="AF24:AK24"/>
+    <mergeCell ref="B64:I64"/>
     <mergeCell ref="Y26:AB26"/>
-    <mergeCell ref="AF33:AK33"/>
-    <mergeCell ref="B97:AK97"/>
     <mergeCell ref="Q24:S24"/>
-    <mergeCell ref="B51:I51"/>
-    <mergeCell ref="C52:AK52"/>
-    <mergeCell ref="B106:AK106"/>
     <mergeCell ref="A1:I1"/>
-    <mergeCell ref="C61:AK61"/>
     <mergeCell ref="T46:X46"/>
-    <mergeCell ref="B63:I63"/>
+    <mergeCell ref="AF53:AK53"/>
+    <mergeCell ref="C36:L36"/>
+    <mergeCell ref="Q51:S51"/>
     <mergeCell ref="M27:P27"/>
+    <mergeCell ref="D52:L52"/>
+    <mergeCell ref="M37:P37"/>
     <mergeCell ref="M36:P36"/>
     <mergeCell ref="Y37:AE37"/>
     <mergeCell ref="T39:X39"/>
-    <mergeCell ref="C81:AK81"/>
     <mergeCell ref="Y27:AB27"/>
+    <mergeCell ref="T48:X48"/>
     <mergeCell ref="AF25:AK25"/>
     <mergeCell ref="J7:AK7"/>
-    <mergeCell ref="Q35:S35"/>
-    <mergeCell ref="C96:AK96"/>
+    <mergeCell ref="Q50:S50"/>
     <mergeCell ref="T32:X32"/>
+    <mergeCell ref="C87:AK87"/>
     <mergeCell ref="T45:X45"/>
+    <mergeCell ref="D102:AK102"/>
     <mergeCell ref="A5:AK5"/>
-    <mergeCell ref="Q34:S34"/>
+    <mergeCell ref="AF30:AK30"/>
     <mergeCell ref="T42:X42"/>
     <mergeCell ref="AF45:AK45"/>
     <mergeCell ref="C28:L28"/>
+    <mergeCell ref="C62:AK62"/>
     <mergeCell ref="Y41:AE41"/>
-    <mergeCell ref="D92:AK92"/>
-    <mergeCell ref="C98:AK98"/>
+    <mergeCell ref="C37:L37"/>
+    <mergeCell ref="T47:X47"/>
     <mergeCell ref="A20:AK20"/>
     <mergeCell ref="AC25:AE25"/>
+    <mergeCell ref="M50:P50"/>
+    <mergeCell ref="M53:P53"/>
     <mergeCell ref="C107:AK107"/>
     <mergeCell ref="B11:I11"/>
     <mergeCell ref="AF42:AK42"/>
     <mergeCell ref="Q27:S27"/>
     <mergeCell ref="Q2:U3"/>
+    <mergeCell ref="Q49:S49"/>
+    <mergeCell ref="T50:X50"/>
     <mergeCell ref="Q36:S36"/>
     <mergeCell ref="T44:X44"/>
-    <mergeCell ref="C64:AK64"/>
-    <mergeCell ref="M34:P34"/>
-    <mergeCell ref="C79:AK79"/>
+    <mergeCell ref="C50:C53"/>
+    <mergeCell ref="C30:L30"/>
+    <mergeCell ref="Q30:S30"/>
+    <mergeCell ref="C116:AK116"/>
     <mergeCell ref="Y43:AE43"/>
-    <mergeCell ref="C73:AK73"/>
+    <mergeCell ref="B67:I67"/>
     <mergeCell ref="J8:AK8"/>
+    <mergeCell ref="B61:I61"/>
+    <mergeCell ref="D94:AK94"/>
+    <mergeCell ref="AF31:AK31"/>
+    <mergeCell ref="B108:AK108"/>
     <mergeCell ref="AF40:AK40"/>
+    <mergeCell ref="M49:P49"/>
     <mergeCell ref="M39:P39"/>
-    <mergeCell ref="B84:AK84"/>
+    <mergeCell ref="M48:P48"/>
+    <mergeCell ref="T51:X51"/>
     <mergeCell ref="T26:X26"/>
+    <mergeCell ref="C93:AK93"/>
     <mergeCell ref="J10:AK10"/>
+    <mergeCell ref="Y30:AB30"/>
     <mergeCell ref="N15:AK15"/>
+    <mergeCell ref="C56:AK56"/>
     <mergeCell ref="T41:X41"/>
-    <mergeCell ref="Y35:AE35"/>
     <mergeCell ref="V1:Y1"/>
     <mergeCell ref="T23:X23"/>
-    <mergeCell ref="C105:AK105"/>
+    <mergeCell ref="Y29:AB29"/>
     <mergeCell ref="Y44:AE44"/>
     <mergeCell ref="J9:AK9"/>
     <mergeCell ref="AF43:AK43"/>
-    <mergeCell ref="B94:AK94"/>
     <mergeCell ref="AH1:AK1"/>
+    <mergeCell ref="D96:AK96"/>
+    <mergeCell ref="M31:P31"/>
+    <mergeCell ref="AC32:AE32"/>
     <mergeCell ref="M40:P40"/>
     <mergeCell ref="T43:X43"/>
+    <mergeCell ref="B55:I55"/>
+    <mergeCell ref="Y31:AB31"/>
     <mergeCell ref="D46:L46"/>
+    <mergeCell ref="T52:X52"/>
     <mergeCell ref="D40:L40"/>
     <mergeCell ref="V2:Y3"/>
     <mergeCell ref="N16:AK16"/>
@@ -6059,56 +6676,71 @@
     <mergeCell ref="C27:L27"/>
     <mergeCell ref="Q38:S38"/>
     <mergeCell ref="Y46:AE46"/>
-    <mergeCell ref="D91:AK91"/>
     <mergeCell ref="AC24:AE24"/>
     <mergeCell ref="B7:I7"/>
     <mergeCell ref="M26:P26"/>
     <mergeCell ref="M41:P41"/>
+    <mergeCell ref="B105:AK105"/>
     <mergeCell ref="Q26:S26"/>
     <mergeCell ref="D41:L41"/>
+    <mergeCell ref="T49:X49"/>
     <mergeCell ref="M24:P24"/>
     <mergeCell ref="Q40:S40"/>
-    <mergeCell ref="C69:AK69"/>
+    <mergeCell ref="B111:AK111"/>
     <mergeCell ref="M38:P38"/>
+    <mergeCell ref="Y48:AE48"/>
     <mergeCell ref="C83:AK83"/>
-    <mergeCell ref="D93:AK93"/>
     <mergeCell ref="AC26:AE26"/>
-    <mergeCell ref="T35:X35"/>
+    <mergeCell ref="C92:AK92"/>
     <mergeCell ref="Y23:AB23"/>
-    <mergeCell ref="D74:AK74"/>
-    <mergeCell ref="Y32:AE32"/>
+    <mergeCell ref="B58:I58"/>
     <mergeCell ref="D43:L43"/>
     <mergeCell ref="T25:X25"/>
     <mergeCell ref="Y42:AE42"/>
-    <mergeCell ref="B60:I60"/>
+    <mergeCell ref="C97:AK97"/>
+    <mergeCell ref="Y47:AE47"/>
     <mergeCell ref="Y38:AE38"/>
     <mergeCell ref="J14:M14"/>
-    <mergeCell ref="B57:I57"/>
-    <mergeCell ref="A30:AK30"/>
+    <mergeCell ref="AF47:AK47"/>
+    <mergeCell ref="M52:P52"/>
+    <mergeCell ref="D100:AK100"/>
     <mergeCell ref="AC27:AE27"/>
-    <mergeCell ref="C43:C46"/>
-    <mergeCell ref="B68:AK68"/>
     <mergeCell ref="AF46:AK46"/>
     <mergeCell ref="AF28:AK28"/>
+    <mergeCell ref="C29:L29"/>
+    <mergeCell ref="D50:L50"/>
+    <mergeCell ref="D84:AK84"/>
     <mergeCell ref="D44:L44"/>
+    <mergeCell ref="Q53:S53"/>
     <mergeCell ref="J15:M15"/>
+    <mergeCell ref="Y51:AE51"/>
     <mergeCell ref="AD1:AG1"/>
     <mergeCell ref="C90:AK90"/>
     <mergeCell ref="AF39:AK39"/>
+    <mergeCell ref="B85:AK85"/>
     <mergeCell ref="Q28:S28"/>
+    <mergeCell ref="AF48:AK48"/>
+    <mergeCell ref="C31:L31"/>
     <mergeCell ref="Q37:S37"/>
     <mergeCell ref="M22:P22"/>
+    <mergeCell ref="C71:AK71"/>
+    <mergeCell ref="Y50:AE50"/>
+    <mergeCell ref="D95:AK95"/>
     <mergeCell ref="AC28:AE28"/>
     <mergeCell ref="C76:AK76"/>
-    <mergeCell ref="B100:AK100"/>
+    <mergeCell ref="M30:P30"/>
+    <mergeCell ref="B75:AK75"/>
+    <mergeCell ref="D104:AK104"/>
     <mergeCell ref="Y22:AB22"/>
-    <mergeCell ref="Y34:AE34"/>
+    <mergeCell ref="Q52:S52"/>
+    <mergeCell ref="C110:AK110"/>
     <mergeCell ref="Q39:S39"/>
     <mergeCell ref="D45:L45"/>
-    <mergeCell ref="D70:AK70"/>
     <mergeCell ref="M28:P28"/>
+    <mergeCell ref="A74:AK74"/>
     <mergeCell ref="M42:P42"/>
-    <mergeCell ref="M37:P37"/>
+    <mergeCell ref="AF29:AK29"/>
+    <mergeCell ref="AC30:AE30"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6281,7 +6913,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/04/13</t>
+          <t>2026/08/17</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -6684,7 +7316,7 @@
       <c r="M14" s="11" t="n"/>
       <c r="N14" s="19" t="inlineStr">
         <is>
-          <t>正常に削除しました</t>
+          <t>削除しました</t>
         </is>
       </c>
       <c r="O14" s="10" t="n"/>
@@ -6874,7 +7506,7 @@
       <c r="M19" s="11" t="n"/>
       <c r="N19" s="19" t="inlineStr">
         <is>
-          <t>関連データが存在するため削除できません</t>
+          <t>関連データが存在するため処理を実行できません</t>
         </is>
       </c>
       <c r="O19" s="10" t="n"/>
@@ -7030,7 +7662,7 @@
       </c>
       <c r="C25" s="19" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>tanka_id</t>
         </is>
       </c>
       <c r="D25" s="10" t="n"/>
@@ -7075,7 +7707,7 @@
       <c r="AE25" s="11" t="n"/>
       <c r="AF25" s="19" t="inlineStr">
         <is>
-          <t>削除対象の tanka_id</t>
+          <t>削除対象の tanka_id（パスパラメータ）</t>
         </is>
       </c>
       <c r="AG25" s="10" t="n"/>
@@ -7279,7 +7911,7 @@
       <c r="C36" s="19" t="inlineStr">
         <is>
           <t>{
-  "message": "正常に削除しました"
+  "message": "削除しました。"
 }</t>
         </is>
       </c>
@@ -7534,7 +8166,7 @@
         <is>
           <t>{
   "error_code": "CONFLICT",
-  "message": "関連データが存在するため削除できません"
+  "message": "関連データが存在するため処理を実行できません"
 }</t>
         </is>
       </c>
@@ -7632,94 +8264,131 @@
         </is>
       </c>
     </row>
-    <row r="58" ht="18" customHeight="1">
-      <c r="B58" s="27" t="inlineStr">
+    <row r="58" ht="54" customHeight="1">
+      <c r="B58" s="42" t="inlineStr">
+        <is>
+          <t>※ 以下の処理は単一トランザクション内で実行する（本処理 + 操作ログ記録）。
+いずれかが失敗した場合は全てロールバックすること。
+例外処理中のエラーログ（log_type=3）はトランザクション外で別途記録する。</t>
+        </is>
+      </c>
+      <c r="C58" s="10" t="n"/>
+      <c r="D58" s="10" t="n"/>
+      <c r="E58" s="10" t="n"/>
+      <c r="F58" s="10" t="n"/>
+      <c r="G58" s="10" t="n"/>
+      <c r="H58" s="10" t="n"/>
+      <c r="I58" s="10" t="n"/>
+      <c r="J58" s="10" t="n"/>
+      <c r="K58" s="10" t="n"/>
+      <c r="L58" s="10" t="n"/>
+      <c r="M58" s="10" t="n"/>
+      <c r="N58" s="10" t="n"/>
+      <c r="O58" s="10" t="n"/>
+      <c r="P58" s="10" t="n"/>
+      <c r="Q58" s="10" t="n"/>
+      <c r="R58" s="10" t="n"/>
+      <c r="S58" s="10" t="n"/>
+      <c r="T58" s="10" t="n"/>
+      <c r="U58" s="10" t="n"/>
+      <c r="V58" s="10" t="n"/>
+      <c r="W58" s="10" t="n"/>
+      <c r="X58" s="10" t="n"/>
+      <c r="Y58" s="10" t="n"/>
+      <c r="Z58" s="10" t="n"/>
+      <c r="AA58" s="10" t="n"/>
+      <c r="AB58" s="10" t="n"/>
+      <c r="AC58" s="10" t="n"/>
+      <c r="AD58" s="10" t="n"/>
+      <c r="AE58" s="10" t="n"/>
+      <c r="AF58" s="10" t="n"/>
+      <c r="AG58" s="10" t="n"/>
+      <c r="AH58" s="10" t="n"/>
+      <c r="AI58" s="10" t="n"/>
+      <c r="AJ58" s="10" t="n"/>
+      <c r="AK58" s="11" t="n"/>
+    </row>
+    <row r="59" ht="18" customHeight="1">
+      <c r="B59" s="27" t="inlineStr">
         <is>
           <t>4.1 リクエストのバリデーション</t>
         </is>
       </c>
     </row>
-    <row r="59" ht="18" customHeight="1">
-      <c r="C59" s="41" t="inlineStr">
+    <row r="60" ht="18" customHeight="1">
+      <c r="C60" s="41" t="inlineStr">
         <is>
           <t>パスパラメータの検証：</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="18" customHeight="1">
-      <c r="D60" s="41" t="inlineStr">
-        <is>
-          <t>id：数値型チェック</t>
         </is>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1">
       <c r="D61" s="41" t="inlineStr">
         <is>
-          <t>id：必須チェック</t>
+          <t>tanka_id：数値型チェック</t>
         </is>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1">
-      <c r="C62" s="41" t="inlineStr">
+      <c r="D62" s="41" t="inlineStr">
+        <is>
+          <t>tanka_id：必須チェック</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="18" customHeight="1">
+      <c r="C63" s="41" t="inlineStr">
         <is>
           <t>不正なパラメータが存在する場合：</t>
         </is>
       </c>
     </row>
-    <row r="63" ht="18" customHeight="1">
-      <c r="D63" s="41" t="inlineStr">
+    <row r="64" ht="18" customHeight="1">
+      <c r="D64" s="41" t="inlineStr">
         <is>
           <t>HTTP 400 Bad Request を返却する。</t>
         </is>
       </c>
     </row>
-    <row r="64" ht="18" customHeight="1">
-      <c r="B64" s="27" t="inlineStr">
+    <row r="65" ht="18" customHeight="1">
+      <c r="B65" s="27" t="inlineStr">
         <is>
           <t>4.2 認証・認可チェック</t>
-        </is>
-      </c>
-    </row>
-    <row r="65" ht="18" customHeight="1">
-      <c r="C65" s="41" t="inlineStr">
-        <is>
-          <t>認証情報を検証する（JWT / Cookie）。</t>
         </is>
       </c>
     </row>
     <row r="66" ht="18" customHeight="1">
       <c r="C66" s="41" t="inlineStr">
         <is>
-          <t>認証失敗の場合：HTTP 401 Unauthorized</t>
+          <t>認証情報を検証する（HTTP-only Cookieセッション）。</t>
         </is>
       </c>
     </row>
     <row r="67" ht="18" customHeight="1">
       <c r="C67" s="41" t="inlineStr">
         <is>
+          <t>認証失敗の場合：HTTP 401 Unauthorized</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="18" customHeight="1">
+      <c r="C68" s="41" t="inlineStr">
+        <is>
           <t>権限チェック：tanka.delete を保持しているか確認する。</t>
         </is>
       </c>
     </row>
-    <row r="68" ht="36" customHeight="1">
-      <c r="D68" s="41" t="inlineStr">
+    <row r="69" ht="36" customHeight="1">
+      <c r="D69" s="41" t="inlineStr">
         <is>
           <t>対象ロール：CHUOKAI（中央会）, JA_HONTEN（JA本店）, JA_KANRI_SHITEN（JA管理支店）</t>
         </is>
       </c>
     </row>
-    <row r="69" ht="18" customHeight="1">
-      <c r="C69" s="41" t="inlineStr">
+    <row r="70" ht="18" customHeight="1">
+      <c r="C70" s="41" t="inlineStr">
         <is>
           <t>権限がない場合：HTTP 403 Forbidden</t>
-        </is>
-      </c>
-    </row>
-    <row r="70" ht="18" customHeight="1">
-      <c r="B70" s="27" t="inlineStr">
-        <is>
-          <t>4.3 データ取得条件の設定</t>
         </is>
       </c>
     </row>
@@ -7740,7 +8409,7 @@
     <row r="73" ht="18" customHeight="1">
       <c r="D73" s="41" t="inlineStr">
         <is>
-          <t>id = {tanka_id} かつ ja_id = user.ja_id</t>
+          <t>tanka_id = :tanka_id かつ ja_id = :ja_id</t>
         </is>
       </c>
     </row>
@@ -7866,7 +8535,7 @@
           <t>UPDATE m_tanka
 SET deleted_at = NOW(),
     updated_by = :user_account_id
-WHERE tanka_id = :id
+WHERE tanka_id = :tanka_id
   AND ja_id = :ja_id
   AND deleted_at IS NULL</t>
         </is>
@@ -8122,7 +8791,9 @@
     <mergeCell ref="N18:AK18"/>
     <mergeCell ref="M29:P29"/>
     <mergeCell ref="J18:M18"/>
+    <mergeCell ref="C68:AK68"/>
     <mergeCell ref="J12:AK12"/>
+    <mergeCell ref="D64:AK64"/>
     <mergeCell ref="N17:AK17"/>
     <mergeCell ref="J17:M17"/>
     <mergeCell ref="D73:AK73"/>
@@ -8134,10 +8805,10 @@
     <mergeCell ref="J1:P1"/>
     <mergeCell ref="AH2:AK3"/>
     <mergeCell ref="Y24:AB24"/>
-    <mergeCell ref="C65:AK65"/>
     <mergeCell ref="C94:AK94"/>
     <mergeCell ref="C75:AK75"/>
     <mergeCell ref="Q1:U1"/>
+    <mergeCell ref="B65:AK65"/>
     <mergeCell ref="C84:AK84"/>
     <mergeCell ref="B10:I10"/>
     <mergeCell ref="C80:AK80"/>
@@ -8148,6 +8819,7 @@
     <mergeCell ref="C95:AK95"/>
     <mergeCell ref="N20:AK20"/>
     <mergeCell ref="M25:P25"/>
+    <mergeCell ref="C70:AK70"/>
     <mergeCell ref="C48:AK48"/>
     <mergeCell ref="Y25:AB25"/>
     <mergeCell ref="D61:AK61"/>
@@ -8158,6 +8830,7 @@
     <mergeCell ref="B77:AK77"/>
     <mergeCell ref="B86:AK86"/>
     <mergeCell ref="Z1:AC1"/>
+    <mergeCell ref="D62:AK62"/>
     <mergeCell ref="N14:AK14"/>
     <mergeCell ref="B12:I12"/>
     <mergeCell ref="C33:AK33"/>
@@ -8167,15 +8840,12 @@
     <mergeCell ref="C24:L24"/>
     <mergeCell ref="AD2:AG3"/>
     <mergeCell ref="B13:I13"/>
-    <mergeCell ref="D63:AK63"/>
     <mergeCell ref="D81:AK81"/>
     <mergeCell ref="Y30:AE30"/>
-    <mergeCell ref="B64:AK64"/>
     <mergeCell ref="J13:AK13"/>
     <mergeCell ref="B14:I20"/>
     <mergeCell ref="Y29:AE29"/>
     <mergeCell ref="C25:L25"/>
-    <mergeCell ref="C59:AK59"/>
     <mergeCell ref="A2:I3"/>
     <mergeCell ref="AF24:AK24"/>
     <mergeCell ref="Q24:S24"/>
@@ -8195,7 +8865,6 @@
     <mergeCell ref="C87:AK87"/>
     <mergeCell ref="A5:AK5"/>
     <mergeCell ref="AF30:AK30"/>
-    <mergeCell ref="C62:AK62"/>
     <mergeCell ref="AC25:AE25"/>
     <mergeCell ref="B11:I11"/>
     <mergeCell ref="C89:AK89"/>
@@ -8205,6 +8874,7 @@
     <mergeCell ref="C79:AK79"/>
     <mergeCell ref="J8:AK8"/>
     <mergeCell ref="C54:AK54"/>
+    <mergeCell ref="C63:AK63"/>
     <mergeCell ref="C93:AK93"/>
     <mergeCell ref="B92:AK92"/>
     <mergeCell ref="J10:AK10"/>
@@ -8222,25 +8892,24 @@
     <mergeCell ref="C67:AK67"/>
     <mergeCell ref="AC24:AE24"/>
     <mergeCell ref="B7:I7"/>
-    <mergeCell ref="B70:AK70"/>
     <mergeCell ref="M24:P24"/>
-    <mergeCell ref="C69:AK69"/>
     <mergeCell ref="C83:AK83"/>
     <mergeCell ref="A22:AK22"/>
     <mergeCell ref="D74:AK74"/>
-    <mergeCell ref="D68:AK68"/>
     <mergeCell ref="T25:X25"/>
     <mergeCell ref="B82:AK82"/>
     <mergeCell ref="J14:M14"/>
-    <mergeCell ref="D60:AK60"/>
     <mergeCell ref="B44:I44"/>
     <mergeCell ref="B53:I53"/>
+    <mergeCell ref="D69:AK69"/>
     <mergeCell ref="C29:L29"/>
     <mergeCell ref="J15:M15"/>
     <mergeCell ref="AD1:AG1"/>
+    <mergeCell ref="C60:AK60"/>
     <mergeCell ref="C71:AK71"/>
     <mergeCell ref="M30:P30"/>
     <mergeCell ref="C91:AK91"/>
+    <mergeCell ref="B59:AK59"/>
     <mergeCell ref="AF29:AK29"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
